--- a/backend/sample_seating_500.xlsx
+++ b/backend/sample_seating_500.xlsx
@@ -415,7 +415,7 @@
         <v>21CS001</v>
       </c>
       <c r="B2" t="str">
-        <v>Arjun Gupta</v>
+        <v>Student 1</v>
       </c>
       <c r="C2" t="str">
         <v>L</v>
@@ -426,10 +426,10 @@
         <v>21CS002</v>
       </c>
       <c r="B3" t="str">
-        <v>Vikram Rathore</v>
+        <v>Student 2</v>
       </c>
       <c r="C3" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="4">
@@ -437,7 +437,7 @@
         <v>21CS003</v>
       </c>
       <c r="B4" t="str">
-        <v>Rohan Yadav</v>
+        <v>Student 3</v>
       </c>
       <c r="C4" t="str">
         <v>L</v>
@@ -448,10 +448,10 @@
         <v>21CS004</v>
       </c>
       <c r="B5" t="str">
-        <v>Rohan Chauhan</v>
+        <v>Student 4</v>
       </c>
       <c r="C5" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="6">
@@ -459,7 +459,7 @@
         <v>21CS005</v>
       </c>
       <c r="B6" t="str">
-        <v>Zara Das</v>
+        <v>Student 5</v>
       </c>
       <c r="C6" t="str">
         <v>L</v>
@@ -470,10 +470,10 @@
         <v>21CS006</v>
       </c>
       <c r="B7" t="str">
-        <v>Sneha Bhatt</v>
+        <v>Student 6</v>
       </c>
       <c r="C7" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="8">
@@ -481,7 +481,7 @@
         <v>21CS007</v>
       </c>
       <c r="B8" t="str">
-        <v>Kavya Reddy</v>
+        <v>Student 7</v>
       </c>
       <c r="C8" t="str">
         <v>L</v>
@@ -492,10 +492,10 @@
         <v>21CS008</v>
       </c>
       <c r="B9" t="str">
-        <v>Zara Gupta</v>
+        <v>Student 8</v>
       </c>
       <c r="C9" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="10">
@@ -503,7 +503,7 @@
         <v>21CS009</v>
       </c>
       <c r="B10" t="str">
-        <v>Swati Das</v>
+        <v>Student 9</v>
       </c>
       <c r="C10" t="str">
         <v>L</v>
@@ -514,10 +514,10 @@
         <v>21CS010</v>
       </c>
       <c r="B11" t="str">
-        <v>Karan Rao</v>
+        <v>Student 10</v>
       </c>
       <c r="C11" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="12">
@@ -525,7 +525,7 @@
         <v>21CS011</v>
       </c>
       <c r="B12" t="str">
-        <v>Rohan Kumar</v>
+        <v>Student 11</v>
       </c>
       <c r="C12" t="str">
         <v>L</v>
@@ -536,10 +536,10 @@
         <v>21CS012</v>
       </c>
       <c r="B13" t="str">
-        <v>Ishaan Patel</v>
+        <v>Student 12</v>
       </c>
       <c r="C13" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="14">
@@ -547,7 +547,7 @@
         <v>21CS013</v>
       </c>
       <c r="B14" t="str">
-        <v>Vikram Verma</v>
+        <v>Student 13</v>
       </c>
       <c r="C14" t="str">
         <v>L</v>
@@ -558,10 +558,10 @@
         <v>21CS014</v>
       </c>
       <c r="B15" t="str">
-        <v>Anjali Yadav</v>
+        <v>Student 14</v>
       </c>
       <c r="C15" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="16">
@@ -569,7 +569,7 @@
         <v>21CS015</v>
       </c>
       <c r="B16" t="str">
-        <v>Aditi Ghosh</v>
+        <v>Student 15</v>
       </c>
       <c r="C16" t="str">
         <v>L</v>
@@ -580,10 +580,10 @@
         <v>21CS016</v>
       </c>
       <c r="B17" t="str">
-        <v>Rahul Rao</v>
+        <v>Student 16</v>
       </c>
       <c r="C17" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="18">
@@ -591,7 +591,7 @@
         <v>21CS017</v>
       </c>
       <c r="B18" t="str">
-        <v>Ishaan Verma</v>
+        <v>Student 17</v>
       </c>
       <c r="C18" t="str">
         <v>L</v>
@@ -602,10 +602,10 @@
         <v>21CS018</v>
       </c>
       <c r="B19" t="str">
-        <v>Pooja Menon</v>
+        <v>Student 18</v>
       </c>
       <c r="C19" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="20">
@@ -613,7 +613,7 @@
         <v>21CS019</v>
       </c>
       <c r="B20" t="str">
-        <v>Siddharth Rathore</v>
+        <v>Student 19</v>
       </c>
       <c r="C20" t="str">
         <v>L</v>
@@ -624,10 +624,10 @@
         <v>21CS020</v>
       </c>
       <c r="B21" t="str">
-        <v>Rahul Sen</v>
+        <v>Student 20</v>
       </c>
       <c r="C21" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="22">
@@ -635,7 +635,7 @@
         <v>21CS021</v>
       </c>
       <c r="B22" t="str">
-        <v>Tarun Patel</v>
+        <v>Student 21</v>
       </c>
       <c r="C22" t="str">
         <v>L</v>
@@ -646,10 +646,10 @@
         <v>21CS022</v>
       </c>
       <c r="B23" t="str">
-        <v>Karan Sharma</v>
+        <v>Student 22</v>
       </c>
       <c r="C23" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="24">
@@ -657,7 +657,7 @@
         <v>21CS023</v>
       </c>
       <c r="B24" t="str">
-        <v>Tarun Joshi</v>
+        <v>Student 23</v>
       </c>
       <c r="C24" t="str">
         <v>L</v>
@@ -668,10 +668,10 @@
         <v>21CS024</v>
       </c>
       <c r="B25" t="str">
-        <v>Pranav Reddy</v>
+        <v>Student 24</v>
       </c>
       <c r="C25" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="26">
@@ -679,7 +679,7 @@
         <v>21CS025</v>
       </c>
       <c r="B26" t="str">
-        <v>Sneha Singh</v>
+        <v>Student 25</v>
       </c>
       <c r="C26" t="str">
         <v>L</v>
@@ -687,21 +687,21 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>21CS026</v>
+        <v>21IT001</v>
       </c>
       <c r="B27" t="str">
-        <v>Riya Rathore</v>
+        <v>Student 26</v>
       </c>
       <c r="C27" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>21CS027</v>
+        <v>21IT002</v>
       </c>
       <c r="B28" t="str">
-        <v>Amit Rao</v>
+        <v>Student 27</v>
       </c>
       <c r="C28" t="str">
         <v>L</v>
@@ -709,21 +709,21 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>21CS028</v>
+        <v>21IT003</v>
       </c>
       <c r="B29" t="str">
-        <v>Sanya Rao</v>
+        <v>Student 28</v>
       </c>
       <c r="C29" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>21CS029</v>
+        <v>21IT004</v>
       </c>
       <c r="B30" t="str">
-        <v>Riya Dutta</v>
+        <v>Student 29</v>
       </c>
       <c r="C30" t="str">
         <v>L</v>
@@ -731,21 +731,21 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>21CS030</v>
+        <v>21IT005</v>
       </c>
       <c r="B31" t="str">
-        <v>Aditi Rathore</v>
+        <v>Student 30</v>
       </c>
       <c r="C31" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>21CS031</v>
+        <v>21IT006</v>
       </c>
       <c r="B32" t="str">
-        <v>Ishaan Rathore</v>
+        <v>Student 31</v>
       </c>
       <c r="C32" t="str">
         <v>L</v>
@@ -753,21 +753,21 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>21CS032</v>
+        <v>21IT007</v>
       </c>
       <c r="B33" t="str">
-        <v>Priya Reddy</v>
+        <v>Student 32</v>
       </c>
       <c r="C33" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>21CS033</v>
+        <v>21IT008</v>
       </c>
       <c r="B34" t="str">
-        <v>Neha Joshi</v>
+        <v>Student 33</v>
       </c>
       <c r="C34" t="str">
         <v>L</v>
@@ -775,21 +775,21 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>21CS034</v>
+        <v>21IT009</v>
       </c>
       <c r="B35" t="str">
-        <v>Rohan Das</v>
+        <v>Student 34</v>
       </c>
       <c r="C35" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>21CS035</v>
+        <v>21IT010</v>
       </c>
       <c r="B36" t="str">
-        <v>Krish Yadav</v>
+        <v>Student 35</v>
       </c>
       <c r="C36" t="str">
         <v>L</v>
@@ -797,21 +797,21 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>21CS036</v>
+        <v>21IT011</v>
       </c>
       <c r="B37" t="str">
-        <v>Pooja Singh</v>
+        <v>Student 36</v>
       </c>
       <c r="C37" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>21CS037</v>
+        <v>21IT012</v>
       </c>
       <c r="B38" t="str">
-        <v>Pranav Rao</v>
+        <v>Student 37</v>
       </c>
       <c r="C38" t="str">
         <v>L</v>
@@ -819,21 +819,21 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>21CS038</v>
+        <v>21IT013</v>
       </c>
       <c r="B39" t="str">
-        <v>Diya Sen</v>
+        <v>Student 38</v>
       </c>
       <c r="C39" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>21CS039</v>
+        <v>21IT014</v>
       </c>
       <c r="B40" t="str">
-        <v>Aditi Desai</v>
+        <v>Student 39</v>
       </c>
       <c r="C40" t="str">
         <v>L</v>
@@ -841,21 +841,21 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>21CS040</v>
+        <v>21IT015</v>
       </c>
       <c r="B41" t="str">
-        <v>Ishaan Rao</v>
+        <v>Student 40</v>
       </c>
       <c r="C41" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>21CS041</v>
+        <v>21IT016</v>
       </c>
       <c r="B42" t="str">
-        <v>Swati Gupta</v>
+        <v>Student 41</v>
       </c>
       <c r="C42" t="str">
         <v>L</v>
@@ -863,21 +863,21 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>21CS042</v>
+        <v>21IT017</v>
       </c>
       <c r="B43" t="str">
-        <v>Sanya Sen</v>
+        <v>Student 42</v>
       </c>
       <c r="C43" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>21CS043</v>
+        <v>21IT018</v>
       </c>
       <c r="B44" t="str">
-        <v>Zara Chauhan</v>
+        <v>Student 43</v>
       </c>
       <c r="C44" t="str">
         <v>L</v>
@@ -885,21 +885,21 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>21CS044</v>
+        <v>21IT019</v>
       </c>
       <c r="B45" t="str">
-        <v>Arjun Reddy</v>
+        <v>Student 44</v>
       </c>
       <c r="C45" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>21CS045</v>
+        <v>21IT020</v>
       </c>
       <c r="B46" t="str">
-        <v>Vikram Iyer</v>
+        <v>Student 45</v>
       </c>
       <c r="C46" t="str">
         <v>L</v>
@@ -907,21 +907,21 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>21CS046</v>
+        <v>21IT021</v>
       </c>
       <c r="B47" t="str">
-        <v>Vikram Rathore</v>
+        <v>Student 46</v>
       </c>
       <c r="C47" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>21CS047</v>
+        <v>21IT022</v>
       </c>
       <c r="B48" t="str">
-        <v>Ishaan Bhatt</v>
+        <v>Student 47</v>
       </c>
       <c r="C48" t="str">
         <v>L</v>
@@ -929,21 +929,21 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>21CS048</v>
+        <v>21IT023</v>
       </c>
       <c r="B49" t="str">
-        <v>Arjun Verma</v>
+        <v>Student 48</v>
       </c>
       <c r="C49" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>21CS049</v>
+        <v>21IT024</v>
       </c>
       <c r="B50" t="str">
-        <v>Priya Sharma</v>
+        <v>Student 49</v>
       </c>
       <c r="C50" t="str">
         <v>L</v>
@@ -951,21 +951,21 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>21CS050</v>
+        <v>21IT025</v>
       </c>
       <c r="B51" t="str">
-        <v>Vikram Singh</v>
+        <v>Student 50</v>
       </c>
       <c r="C51" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>21CS051</v>
+        <v>21ECE001</v>
       </c>
       <c r="B52" t="str">
-        <v>Rohan Chauhan</v>
+        <v>Student 51</v>
       </c>
       <c r="C52" t="str">
         <v>L</v>
@@ -973,21 +973,21 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>21CS052</v>
+        <v>21ECE002</v>
       </c>
       <c r="B53" t="str">
-        <v>Arjun Verma</v>
+        <v>Student 52</v>
       </c>
       <c r="C53" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>21CS053</v>
+        <v>21ECE003</v>
       </c>
       <c r="B54" t="str">
-        <v>Amit Verma</v>
+        <v>Student 53</v>
       </c>
       <c r="C54" t="str">
         <v>L</v>
@@ -995,21 +995,21 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>21CS054</v>
+        <v>21ECE004</v>
       </c>
       <c r="B55" t="str">
-        <v>Vikram Bhatt</v>
+        <v>Student 54</v>
       </c>
       <c r="C55" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>21CS055</v>
+        <v>21ECE005</v>
       </c>
       <c r="B56" t="str">
-        <v>Riya Rathore</v>
+        <v>Student 55</v>
       </c>
       <c r="C56" t="str">
         <v>L</v>
@@ -1017,21 +1017,21 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>21CS056</v>
+        <v>21ECE006</v>
       </c>
       <c r="B57" t="str">
-        <v>Neha Joshi</v>
+        <v>Student 56</v>
       </c>
       <c r="C57" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>21CS057</v>
+        <v>21ECE007</v>
       </c>
       <c r="B58" t="str">
-        <v>Rahul Bhatt</v>
+        <v>Student 57</v>
       </c>
       <c r="C58" t="str">
         <v>L</v>
@@ -1039,21 +1039,21 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>21CS058</v>
+        <v>21ECE008</v>
       </c>
       <c r="B59" t="str">
-        <v>Anjali Yadav</v>
+        <v>Student 58</v>
       </c>
       <c r="C59" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>21CS059</v>
+        <v>21ECE009</v>
       </c>
       <c r="B60" t="str">
-        <v>Diya Joshi</v>
+        <v>Student 59</v>
       </c>
       <c r="C60" t="str">
         <v>L</v>
@@ -1061,21 +1061,21 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>21CS060</v>
+        <v>21ECE010</v>
       </c>
       <c r="B61" t="str">
-        <v>Sneha Bose</v>
+        <v>Student 60</v>
       </c>
       <c r="C61" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>21CS061</v>
+        <v>21ECE011</v>
       </c>
       <c r="B62" t="str">
-        <v>Zara Reddy</v>
+        <v>Student 61</v>
       </c>
       <c r="C62" t="str">
         <v>L</v>
@@ -1083,21 +1083,21 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>21CS062</v>
+        <v>21ECE012</v>
       </c>
       <c r="B63" t="str">
-        <v>Swati Bhatt</v>
+        <v>Student 62</v>
       </c>
       <c r="C63" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>21CS063</v>
+        <v>21ECE013</v>
       </c>
       <c r="B64" t="str">
-        <v>Vikram Ghosh</v>
+        <v>Student 63</v>
       </c>
       <c r="C64" t="str">
         <v>L</v>
@@ -1105,21 +1105,21 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>21CS064</v>
+        <v>21ECE014</v>
       </c>
       <c r="B65" t="str">
-        <v>Priya Reddy</v>
+        <v>Student 64</v>
       </c>
       <c r="C65" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>21CS065</v>
+        <v>21ECE015</v>
       </c>
       <c r="B66" t="str">
-        <v>Diya Iyer</v>
+        <v>Student 65</v>
       </c>
       <c r="C66" t="str">
         <v>L</v>
@@ -1127,21 +1127,21 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>21CS066</v>
+        <v>21ECE016</v>
       </c>
       <c r="B67" t="str">
-        <v>Aarav Rao</v>
+        <v>Student 66</v>
       </c>
       <c r="C67" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>21CS067</v>
+        <v>21ECE017</v>
       </c>
       <c r="B68" t="str">
-        <v>Swati Bhatt</v>
+        <v>Student 67</v>
       </c>
       <c r="C68" t="str">
         <v>L</v>
@@ -1149,21 +1149,21 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>21CS068</v>
+        <v>21ECE018</v>
       </c>
       <c r="B69" t="str">
-        <v>Priya Bose</v>
+        <v>Student 68</v>
       </c>
       <c r="C69" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>21CS069</v>
+        <v>21ECE019</v>
       </c>
       <c r="B70" t="str">
-        <v>Krish Reddy</v>
+        <v>Student 69</v>
       </c>
       <c r="C70" t="str">
         <v>L</v>
@@ -1171,21 +1171,21 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>21CS070</v>
+        <v>21ECE020</v>
       </c>
       <c r="B71" t="str">
-        <v>Pooja Sharma</v>
+        <v>Student 70</v>
       </c>
       <c r="C71" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>21CS071</v>
+        <v>21ECE021</v>
       </c>
       <c r="B72" t="str">
-        <v>Pooja Desai</v>
+        <v>Student 71</v>
       </c>
       <c r="C72" t="str">
         <v>L</v>
@@ -1193,21 +1193,21 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>21CS072</v>
+        <v>21ECE022</v>
       </c>
       <c r="B73" t="str">
-        <v>Anjali Joshi</v>
+        <v>Student 72</v>
       </c>
       <c r="C73" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>21CS073</v>
+        <v>21ECE023</v>
       </c>
       <c r="B74" t="str">
-        <v>Kavya Ghosh</v>
+        <v>Student 73</v>
       </c>
       <c r="C74" t="str">
         <v>L</v>
@@ -1215,21 +1215,21 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>21CS074</v>
+        <v>21ECE024</v>
       </c>
       <c r="B75" t="str">
-        <v>Diya Das</v>
+        <v>Student 74</v>
       </c>
       <c r="C75" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>21CS075</v>
+        <v>21ECE025</v>
       </c>
       <c r="B76" t="str">
-        <v>Arjun Desai</v>
+        <v>Student 75</v>
       </c>
       <c r="C76" t="str">
         <v>L</v>
@@ -1237,21 +1237,21 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>21CS076</v>
+        <v>21MECH001</v>
       </c>
       <c r="B77" t="str">
-        <v>Kavya Menon</v>
+        <v>Student 76</v>
       </c>
       <c r="C77" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>21CS077</v>
+        <v>21MECH002</v>
       </c>
       <c r="B78" t="str">
-        <v>Sneha Pillai</v>
+        <v>Student 77</v>
       </c>
       <c r="C78" t="str">
         <v>L</v>
@@ -1259,21 +1259,21 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>21CS078</v>
+        <v>21MECH003</v>
       </c>
       <c r="B79" t="str">
-        <v>Pooja Menon</v>
+        <v>Student 78</v>
       </c>
       <c r="C79" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>21CS079</v>
+        <v>21MECH004</v>
       </c>
       <c r="B80" t="str">
-        <v>Aditi Menon</v>
+        <v>Student 79</v>
       </c>
       <c r="C80" t="str">
         <v>L</v>
@@ -1281,21 +1281,21 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>21CS080</v>
+        <v>21MECH005</v>
       </c>
       <c r="B81" t="str">
-        <v>Kavya Das</v>
+        <v>Student 80</v>
       </c>
       <c r="C81" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>21CS081</v>
+        <v>21MECH006</v>
       </c>
       <c r="B82" t="str">
-        <v>Anjali Bhatt</v>
+        <v>Student 81</v>
       </c>
       <c r="C82" t="str">
         <v>L</v>
@@ -1303,21 +1303,21 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>21CS082</v>
+        <v>21MECH007</v>
       </c>
       <c r="B83" t="str">
-        <v>Priya Ghosh</v>
+        <v>Student 82</v>
       </c>
       <c r="C83" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>21CS083</v>
+        <v>21MECH008</v>
       </c>
       <c r="B84" t="str">
-        <v>Anjali Menon</v>
+        <v>Student 83</v>
       </c>
       <c r="C84" t="str">
         <v>L</v>
@@ -1325,21 +1325,21 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>21CS084</v>
+        <v>21MECH009</v>
       </c>
       <c r="B85" t="str">
-        <v>Rahul Bose</v>
+        <v>Student 84</v>
       </c>
       <c r="C85" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>21CS085</v>
+        <v>21MECH010</v>
       </c>
       <c r="B86" t="str">
-        <v>Amit Gupta</v>
+        <v>Student 85</v>
       </c>
       <c r="C86" t="str">
         <v>L</v>
@@ -1347,21 +1347,21 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>21CS086</v>
+        <v>21MECH011</v>
       </c>
       <c r="B87" t="str">
-        <v>Vihaan Joshi</v>
+        <v>Student 86</v>
       </c>
       <c r="C87" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>21CS087</v>
+        <v>21MECH012</v>
       </c>
       <c r="B88" t="str">
-        <v>Vikram Dutta</v>
+        <v>Student 87</v>
       </c>
       <c r="C88" t="str">
         <v>L</v>
@@ -1369,21 +1369,21 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>21CS088</v>
+        <v>21MECH013</v>
       </c>
       <c r="B89" t="str">
-        <v>Rohan Gupta</v>
+        <v>Student 88</v>
       </c>
       <c r="C89" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>21CS089</v>
+        <v>21MECH014</v>
       </c>
       <c r="B90" t="str">
-        <v>Krish Nair</v>
+        <v>Student 89</v>
       </c>
       <c r="C90" t="str">
         <v>L</v>
@@ -1391,21 +1391,21 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>21CS090</v>
+        <v>21MECH015</v>
       </c>
       <c r="B91" t="str">
-        <v>Tarun Singh</v>
+        <v>Student 90</v>
       </c>
       <c r="C91" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>21CS091</v>
+        <v>21MECH016</v>
       </c>
       <c r="B92" t="str">
-        <v>Krish Rao</v>
+        <v>Student 91</v>
       </c>
       <c r="C92" t="str">
         <v>L</v>
@@ -1413,21 +1413,21 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>21CS092</v>
+        <v>21MECH017</v>
       </c>
       <c r="B93" t="str">
-        <v>Karan Bose</v>
+        <v>Student 92</v>
       </c>
       <c r="C93" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>21CS093</v>
+        <v>21MECH018</v>
       </c>
       <c r="B94" t="str">
-        <v>Siddharth Yadav</v>
+        <v>Student 93</v>
       </c>
       <c r="C94" t="str">
         <v>L</v>
@@ -1435,21 +1435,21 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>21CS094</v>
+        <v>21MECH019</v>
       </c>
       <c r="B95" t="str">
-        <v>Pranav Bose</v>
+        <v>Student 94</v>
       </c>
       <c r="C95" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>21CS095</v>
+        <v>21MECH020</v>
       </c>
       <c r="B96" t="str">
-        <v>Priya Yadav</v>
+        <v>Student 95</v>
       </c>
       <c r="C96" t="str">
         <v>L</v>
@@ -1457,21 +1457,21 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>21CS096</v>
+        <v>21MECH021</v>
       </c>
       <c r="B97" t="str">
-        <v>Siddharth Patel</v>
+        <v>Student 96</v>
       </c>
       <c r="C97" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>21CS097</v>
+        <v>21MECH022</v>
       </c>
       <c r="B98" t="str">
-        <v>Diya Sharma</v>
+        <v>Student 97</v>
       </c>
       <c r="C98" t="str">
         <v>L</v>
@@ -1479,21 +1479,21 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>21CS098</v>
+        <v>21MECH023</v>
       </c>
       <c r="B99" t="str">
-        <v>Pranav Iyer</v>
+        <v>Student 98</v>
       </c>
       <c r="C99" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>21CS099</v>
+        <v>21MECH024</v>
       </c>
       <c r="B100" t="str">
-        <v>Anjali Singh</v>
+        <v>Student 99</v>
       </c>
       <c r="C100" t="str">
         <v>L</v>
@@ -1501,21 +1501,21 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>21CS100</v>
+        <v>21MECH025</v>
       </c>
       <c r="B101" t="str">
-        <v>Sneha Bose</v>
+        <v>Student 100</v>
       </c>
       <c r="C101" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>21CS101</v>
+        <v>21CIVIL001</v>
       </c>
       <c r="B102" t="str">
-        <v>Anjali Joshi</v>
+        <v>Student 101</v>
       </c>
       <c r="C102" t="str">
         <v>L</v>
@@ -1523,21 +1523,21 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>21CS102</v>
+        <v>21CIVIL002</v>
       </c>
       <c r="B103" t="str">
-        <v>Ishaan Rao</v>
+        <v>Student 102</v>
       </c>
       <c r="C103" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>21CS103</v>
+        <v>21CIVIL003</v>
       </c>
       <c r="B104" t="str">
-        <v>Pranav Pillai</v>
+        <v>Student 103</v>
       </c>
       <c r="C104" t="str">
         <v>L</v>
@@ -1545,21 +1545,21 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>21CS104</v>
+        <v>21CIVIL004</v>
       </c>
       <c r="B105" t="str">
-        <v>Neha Yadav</v>
+        <v>Student 104</v>
       </c>
       <c r="C105" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>21CS105</v>
+        <v>21CIVIL005</v>
       </c>
       <c r="B106" t="str">
-        <v>Aditi Singh</v>
+        <v>Student 105</v>
       </c>
       <c r="C106" t="str">
         <v>L</v>
@@ -1567,21 +1567,21 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>21CS106</v>
+        <v>21CIVIL006</v>
       </c>
       <c r="B107" t="str">
-        <v>Rahul Rathore</v>
+        <v>Student 106</v>
       </c>
       <c r="C107" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>21CS107</v>
+        <v>21CIVIL007</v>
       </c>
       <c r="B108" t="str">
-        <v>Sneha Kumar</v>
+        <v>Student 107</v>
       </c>
       <c r="C108" t="str">
         <v>L</v>
@@ -1589,21 +1589,21 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>21CS108</v>
+        <v>21CIVIL008</v>
       </c>
       <c r="B109" t="str">
-        <v>Tarun Singh</v>
+        <v>Student 108</v>
       </c>
       <c r="C109" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>21CS109</v>
+        <v>21CIVIL009</v>
       </c>
       <c r="B110" t="str">
-        <v>Vikram Bhatt</v>
+        <v>Student 109</v>
       </c>
       <c r="C110" t="str">
         <v>L</v>
@@ -1611,21 +1611,21 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>21CS110</v>
+        <v>21CIVIL010</v>
       </c>
       <c r="B111" t="str">
-        <v>Sanya Pillai</v>
+        <v>Student 110</v>
       </c>
       <c r="C111" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>21CS111</v>
+        <v>21CIVIL011</v>
       </c>
       <c r="B112" t="str">
-        <v>Ishaan Bose</v>
+        <v>Student 111</v>
       </c>
       <c r="C112" t="str">
         <v>L</v>
@@ -1633,21 +1633,21 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>21CS112</v>
+        <v>21CIVIL012</v>
       </c>
       <c r="B113" t="str">
-        <v>Riya Gupta</v>
+        <v>Student 112</v>
       </c>
       <c r="C113" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>21CS113</v>
+        <v>21CIVIL013</v>
       </c>
       <c r="B114" t="str">
-        <v>Priya Kumar</v>
+        <v>Student 113</v>
       </c>
       <c r="C114" t="str">
         <v>L</v>
@@ -1655,21 +1655,21 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>21CS114</v>
+        <v>21CIVIL014</v>
       </c>
       <c r="B115" t="str">
-        <v>Kavya Reddy</v>
+        <v>Student 114</v>
       </c>
       <c r="C115" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>21CS115</v>
+        <v>21CIVIL015</v>
       </c>
       <c r="B116" t="str">
-        <v>Neha Das</v>
+        <v>Student 115</v>
       </c>
       <c r="C116" t="str">
         <v>L</v>
@@ -1677,21 +1677,21 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>21CS116</v>
+        <v>21CIVIL016</v>
       </c>
       <c r="B117" t="str">
-        <v>Neha Verma</v>
+        <v>Student 116</v>
       </c>
       <c r="C117" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>21CS117</v>
+        <v>21CIVIL017</v>
       </c>
       <c r="B118" t="str">
-        <v>Anjali Desai</v>
+        <v>Student 117</v>
       </c>
       <c r="C118" t="str">
         <v>L</v>
@@ -1699,21 +1699,21 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>21CS118</v>
+        <v>21CIVIL018</v>
       </c>
       <c r="B119" t="str">
-        <v>Krish Rao</v>
+        <v>Student 118</v>
       </c>
       <c r="C119" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>21CS119</v>
+        <v>21CIVIL019</v>
       </c>
       <c r="B120" t="str">
-        <v>Kavya Reddy</v>
+        <v>Student 119</v>
       </c>
       <c r="C120" t="str">
         <v>L</v>
@@ -1721,21 +1721,21 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>21CS120</v>
+        <v>21CIVIL020</v>
       </c>
       <c r="B121" t="str">
-        <v>Sneha Iyer</v>
+        <v>Student 120</v>
       </c>
       <c r="C121" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>21CS121</v>
+        <v>21CIVIL021</v>
       </c>
       <c r="B122" t="str">
-        <v>Kavya Pillai</v>
+        <v>Student 121</v>
       </c>
       <c r="C122" t="str">
         <v>L</v>
@@ -1743,21 +1743,21 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>21CS122</v>
+        <v>21CIVIL022</v>
       </c>
       <c r="B123" t="str">
-        <v>Rohan Desai</v>
+        <v>Student 122</v>
       </c>
       <c r="C123" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>21CS123</v>
+        <v>21CIVIL023</v>
       </c>
       <c r="B124" t="str">
-        <v>Kavya Das</v>
+        <v>Student 123</v>
       </c>
       <c r="C124" t="str">
         <v>L</v>
@@ -1765,21 +1765,21 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>21CS124</v>
+        <v>21CIVIL024</v>
       </c>
       <c r="B125" t="str">
-        <v>Aarav Pillai</v>
+        <v>Student 124</v>
       </c>
       <c r="C125" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>21CS125</v>
+        <v>21CIVIL025</v>
       </c>
       <c r="B126" t="str">
-        <v>Vikram Yadav</v>
+        <v>Student 125</v>
       </c>
       <c r="C126" t="str">
         <v>L</v>
@@ -1787,21 +1787,21 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>21CS126</v>
+        <v>22CS001</v>
       </c>
       <c r="B127" t="str">
-        <v>Priya Ghosh</v>
+        <v>Student 126</v>
       </c>
       <c r="C127" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>21CS127</v>
+        <v>22CS002</v>
       </c>
       <c r="B128" t="str">
-        <v>Vikram Patel</v>
+        <v>Student 127</v>
       </c>
       <c r="C128" t="str">
         <v>L</v>
@@ -1809,21 +1809,21 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>21CS128</v>
+        <v>22CS003</v>
       </c>
       <c r="B129" t="str">
-        <v>Arjun Yadav</v>
+        <v>Student 128</v>
       </c>
       <c r="C129" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>21CS129</v>
+        <v>22CS004</v>
       </c>
       <c r="B130" t="str">
-        <v>Swati Bose</v>
+        <v>Student 129</v>
       </c>
       <c r="C130" t="str">
         <v>L</v>
@@ -1831,21 +1831,21 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>21CS130</v>
+        <v>22CS005</v>
       </c>
       <c r="B131" t="str">
-        <v>Neha Reddy</v>
+        <v>Student 130</v>
       </c>
       <c r="C131" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>21CS131</v>
+        <v>22CS006</v>
       </c>
       <c r="B132" t="str">
-        <v>Krish Dutta</v>
+        <v>Student 131</v>
       </c>
       <c r="C132" t="str">
         <v>L</v>
@@ -1853,21 +1853,21 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>21CS132</v>
+        <v>22CS007</v>
       </c>
       <c r="B133" t="str">
-        <v>Krish Iyer</v>
+        <v>Student 132</v>
       </c>
       <c r="C133" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>21CS133</v>
+        <v>22CS008</v>
       </c>
       <c r="B134" t="str">
-        <v>Neha Dutta</v>
+        <v>Student 133</v>
       </c>
       <c r="C134" t="str">
         <v>L</v>
@@ -1875,21 +1875,21 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>21CS134</v>
+        <v>22CS009</v>
       </c>
       <c r="B135" t="str">
-        <v>Rahul Nair</v>
+        <v>Student 134</v>
       </c>
       <c r="C135" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>21CS135</v>
+        <v>22CS010</v>
       </c>
       <c r="B136" t="str">
-        <v>Anjali Reddy</v>
+        <v>Student 135</v>
       </c>
       <c r="C136" t="str">
         <v>L</v>
@@ -1897,21 +1897,21 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>21CS136</v>
+        <v>22CS011</v>
       </c>
       <c r="B137" t="str">
-        <v>Pranav Dutta</v>
+        <v>Student 136</v>
       </c>
       <c r="C137" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>21CS137</v>
+        <v>22CS012</v>
       </c>
       <c r="B138" t="str">
-        <v>Aarav Joshi</v>
+        <v>Student 137</v>
       </c>
       <c r="C138" t="str">
         <v>L</v>
@@ -1919,21 +1919,21 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>21CS138</v>
+        <v>22CS013</v>
       </c>
       <c r="B139" t="str">
-        <v>Neha Verma</v>
+        <v>Student 138</v>
       </c>
       <c r="C139" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>21CS139</v>
+        <v>22CS014</v>
       </c>
       <c r="B140" t="str">
-        <v>Neha Chauhan</v>
+        <v>Student 139</v>
       </c>
       <c r="C140" t="str">
         <v>L</v>
@@ -1941,21 +1941,21 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>21CS140</v>
+        <v>22CS015</v>
       </c>
       <c r="B141" t="str">
-        <v>Arjun Ghosh</v>
+        <v>Student 140</v>
       </c>
       <c r="C141" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>21CS141</v>
+        <v>22CS016</v>
       </c>
       <c r="B142" t="str">
-        <v>Vihaan Rathore</v>
+        <v>Student 141</v>
       </c>
       <c r="C142" t="str">
         <v>L</v>
@@ -1963,21 +1963,21 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>21CS142</v>
+        <v>22CS017</v>
       </c>
       <c r="B143" t="str">
-        <v>Arjun Rathore</v>
+        <v>Student 142</v>
       </c>
       <c r="C143" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>21CS143</v>
+        <v>22CS018</v>
       </c>
       <c r="B144" t="str">
-        <v>Pranav Nair</v>
+        <v>Student 143</v>
       </c>
       <c r="C144" t="str">
         <v>L</v>
@@ -1985,21 +1985,21 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>21CS144</v>
+        <v>22CS019</v>
       </c>
       <c r="B145" t="str">
-        <v>Tarun Reddy</v>
+        <v>Student 144</v>
       </c>
       <c r="C145" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>21CS145</v>
+        <v>22CS020</v>
       </c>
       <c r="B146" t="str">
-        <v>Pooja Menon</v>
+        <v>Student 145</v>
       </c>
       <c r="C146" t="str">
         <v>L</v>
@@ -2007,21 +2007,21 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>21CS146</v>
+        <v>22CS021</v>
       </c>
       <c r="B147" t="str">
-        <v>Vikram Pillai</v>
+        <v>Student 146</v>
       </c>
       <c r="C147" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>21CS147</v>
+        <v>22CS022</v>
       </c>
       <c r="B148" t="str">
-        <v>Zara Mishra</v>
+        <v>Student 147</v>
       </c>
       <c r="C148" t="str">
         <v>L</v>
@@ -2029,21 +2029,21 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>21CS148</v>
+        <v>22CS023</v>
       </c>
       <c r="B149" t="str">
-        <v>Neha Singh</v>
+        <v>Student 148</v>
       </c>
       <c r="C149" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>21CS149</v>
+        <v>22CS024</v>
       </c>
       <c r="B150" t="str">
-        <v>Aarav Singh</v>
+        <v>Student 149</v>
       </c>
       <c r="C150" t="str">
         <v>L</v>
@@ -2051,21 +2051,21 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>21CS150</v>
+        <v>22CS025</v>
       </c>
       <c r="B151" t="str">
-        <v>Krish Das</v>
+        <v>Student 150</v>
       </c>
       <c r="C151" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>21CS151</v>
+        <v>22IT001</v>
       </c>
       <c r="B152" t="str">
-        <v>Arjun Dutta</v>
+        <v>Student 151</v>
       </c>
       <c r="C152" t="str">
         <v>L</v>
@@ -2073,21 +2073,21 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>21CS152</v>
+        <v>22IT002</v>
       </c>
       <c r="B153" t="str">
-        <v>Pranav Pillai</v>
+        <v>Student 152</v>
       </c>
       <c r="C153" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>21CS153</v>
+        <v>22IT003</v>
       </c>
       <c r="B154" t="str">
-        <v>Neha Iyer</v>
+        <v>Student 153</v>
       </c>
       <c r="C154" t="str">
         <v>L</v>
@@ -2095,21 +2095,21 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>21CS154</v>
+        <v>22IT004</v>
       </c>
       <c r="B155" t="str">
-        <v>Rohan Mishra</v>
+        <v>Student 154</v>
       </c>
       <c r="C155" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>21CS155</v>
+        <v>22IT005</v>
       </c>
       <c r="B156" t="str">
-        <v>Ishaan Ghosh</v>
+        <v>Student 155</v>
       </c>
       <c r="C156" t="str">
         <v>L</v>
@@ -2117,21 +2117,21 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>21CS156</v>
+        <v>22IT006</v>
       </c>
       <c r="B157" t="str">
-        <v>Tarun Bose</v>
+        <v>Student 156</v>
       </c>
       <c r="C157" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>21CS157</v>
+        <v>22IT007</v>
       </c>
       <c r="B158" t="str">
-        <v>Priya Iyer</v>
+        <v>Student 157</v>
       </c>
       <c r="C158" t="str">
         <v>L</v>
@@ -2139,21 +2139,21 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>21CS158</v>
+        <v>22IT008</v>
       </c>
       <c r="B159" t="str">
-        <v>Sanya Bhatt</v>
+        <v>Student 158</v>
       </c>
       <c r="C159" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>21CS159</v>
+        <v>22IT009</v>
       </c>
       <c r="B160" t="str">
-        <v>Pooja Das</v>
+        <v>Student 159</v>
       </c>
       <c r="C160" t="str">
         <v>L</v>
@@ -2161,21 +2161,21 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>21CS160</v>
+        <v>22IT010</v>
       </c>
       <c r="B161" t="str">
-        <v>Rahul Reddy</v>
+        <v>Student 160</v>
       </c>
       <c r="C161" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>21CS161</v>
+        <v>22IT011</v>
       </c>
       <c r="B162" t="str">
-        <v>Siddharth Pillai</v>
+        <v>Student 161</v>
       </c>
       <c r="C162" t="str">
         <v>L</v>
@@ -2183,21 +2183,21 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>21CS162</v>
+        <v>22IT012</v>
       </c>
       <c r="B163" t="str">
-        <v>Zara Dutta</v>
+        <v>Student 162</v>
       </c>
       <c r="C163" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>21CS163</v>
+        <v>22IT013</v>
       </c>
       <c r="B164" t="str">
-        <v>Arjun Chauhan</v>
+        <v>Student 163</v>
       </c>
       <c r="C164" t="str">
         <v>L</v>
@@ -2205,21 +2205,21 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>21CS164</v>
+        <v>22IT014</v>
       </c>
       <c r="B165" t="str">
-        <v>Pooja Sharma</v>
+        <v>Student 164</v>
       </c>
       <c r="C165" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>21CS165</v>
+        <v>22IT015</v>
       </c>
       <c r="B166" t="str">
-        <v>Arjun Yadav</v>
+        <v>Student 165</v>
       </c>
       <c r="C166" t="str">
         <v>L</v>
@@ -2227,21 +2227,21 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>21CS166</v>
+        <v>22IT016</v>
       </c>
       <c r="B167" t="str">
-        <v>Priya Rao</v>
+        <v>Student 166</v>
       </c>
       <c r="C167" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>21CS167</v>
+        <v>22IT017</v>
       </c>
       <c r="B168" t="str">
-        <v>Anjali Das</v>
+        <v>Student 167</v>
       </c>
       <c r="C168" t="str">
         <v>L</v>
@@ -2249,21 +2249,21 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>21CS168</v>
+        <v>22IT018</v>
       </c>
       <c r="B169" t="str">
-        <v>Zara Sen</v>
+        <v>Student 168</v>
       </c>
       <c r="C169" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>21CS169</v>
+        <v>22IT019</v>
       </c>
       <c r="B170" t="str">
-        <v>Vikram Sharma</v>
+        <v>Student 169</v>
       </c>
       <c r="C170" t="str">
         <v>L</v>
@@ -2271,21 +2271,21 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>21CS170</v>
+        <v>22IT020</v>
       </c>
       <c r="B171" t="str">
-        <v>Sneha Ghosh</v>
+        <v>Student 170</v>
       </c>
       <c r="C171" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>21CS171</v>
+        <v>22IT021</v>
       </c>
       <c r="B172" t="str">
-        <v>Anjali Menon</v>
+        <v>Student 171</v>
       </c>
       <c r="C172" t="str">
         <v>L</v>
@@ -2293,21 +2293,21 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>21CS172</v>
+        <v>22IT022</v>
       </c>
       <c r="B173" t="str">
-        <v>Tarun Singh</v>
+        <v>Student 172</v>
       </c>
       <c r="C173" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>21CS173</v>
+        <v>22IT023</v>
       </c>
       <c r="B174" t="str">
-        <v>Pooja Rao</v>
+        <v>Student 173</v>
       </c>
       <c r="C174" t="str">
         <v>L</v>
@@ -2315,21 +2315,21 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>21CS174</v>
+        <v>22IT024</v>
       </c>
       <c r="B175" t="str">
-        <v>Diya Ghosh</v>
+        <v>Student 174</v>
       </c>
       <c r="C175" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>21CS175</v>
+        <v>22IT025</v>
       </c>
       <c r="B176" t="str">
-        <v>Sanya Rathore</v>
+        <v>Student 175</v>
       </c>
       <c r="C176" t="str">
         <v>L</v>
@@ -2337,21 +2337,21 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>21CS176</v>
+        <v>22ECE001</v>
       </c>
       <c r="B177" t="str">
-        <v>Zara Nair</v>
+        <v>Student 176</v>
       </c>
       <c r="C177" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>21CS177</v>
+        <v>22ECE002</v>
       </c>
       <c r="B178" t="str">
-        <v>Sneha Sen</v>
+        <v>Student 177</v>
       </c>
       <c r="C178" t="str">
         <v>L</v>
@@ -2359,21 +2359,21 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>21CS178</v>
+        <v>22ECE003</v>
       </c>
       <c r="B179" t="str">
-        <v>Ishaan Iyer</v>
+        <v>Student 178</v>
       </c>
       <c r="C179" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>21CS179</v>
+        <v>22ECE004</v>
       </c>
       <c r="B180" t="str">
-        <v>Rahul Joshi</v>
+        <v>Student 179</v>
       </c>
       <c r="C180" t="str">
         <v>L</v>
@@ -2381,21 +2381,21 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>21CS180</v>
+        <v>22ECE005</v>
       </c>
       <c r="B181" t="str">
-        <v>Aarav Rathore</v>
+        <v>Student 180</v>
       </c>
       <c r="C181" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>21CS181</v>
+        <v>22ECE006</v>
       </c>
       <c r="B182" t="str">
-        <v>Swati Mishra</v>
+        <v>Student 181</v>
       </c>
       <c r="C182" t="str">
         <v>L</v>
@@ -2403,21 +2403,21 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>21CS182</v>
+        <v>22ECE007</v>
       </c>
       <c r="B183" t="str">
-        <v>Amit Patel</v>
+        <v>Student 182</v>
       </c>
       <c r="C183" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>21CS183</v>
+        <v>22ECE008</v>
       </c>
       <c r="B184" t="str">
-        <v>Sanya Menon</v>
+        <v>Student 183</v>
       </c>
       <c r="C184" t="str">
         <v>L</v>
@@ -2425,21 +2425,21 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>21CS184</v>
+        <v>22ECE009</v>
       </c>
       <c r="B185" t="str">
-        <v>Tarun Das</v>
+        <v>Student 184</v>
       </c>
       <c r="C185" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>21CS185</v>
+        <v>22ECE010</v>
       </c>
       <c r="B186" t="str">
-        <v>Siddharth Yadav</v>
+        <v>Student 185</v>
       </c>
       <c r="C186" t="str">
         <v>L</v>
@@ -2447,21 +2447,21 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>21CS186</v>
+        <v>22ECE011</v>
       </c>
       <c r="B187" t="str">
-        <v>Aditi Verma</v>
+        <v>Student 186</v>
       </c>
       <c r="C187" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>21CS187</v>
+        <v>22ECE012</v>
       </c>
       <c r="B188" t="str">
-        <v>Amit Sharma</v>
+        <v>Student 187</v>
       </c>
       <c r="C188" t="str">
         <v>L</v>
@@ -2469,21 +2469,21 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>21CS188</v>
+        <v>22ECE013</v>
       </c>
       <c r="B189" t="str">
-        <v>Anjali Chauhan</v>
+        <v>Student 188</v>
       </c>
       <c r="C189" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>21CS189</v>
+        <v>22ECE014</v>
       </c>
       <c r="B190" t="str">
-        <v>Siddharth Dutta</v>
+        <v>Student 189</v>
       </c>
       <c r="C190" t="str">
         <v>L</v>
@@ -2491,21 +2491,21 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>21CS190</v>
+        <v>22ECE015</v>
       </c>
       <c r="B191" t="str">
-        <v>Karan Ghosh</v>
+        <v>Student 190</v>
       </c>
       <c r="C191" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>21CS191</v>
+        <v>22ECE016</v>
       </c>
       <c r="B192" t="str">
-        <v>Krish Ghosh</v>
+        <v>Student 191</v>
       </c>
       <c r="C192" t="str">
         <v>L</v>
@@ -2513,21 +2513,21 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>21CS192</v>
+        <v>22ECE017</v>
       </c>
       <c r="B193" t="str">
-        <v>Pranav Menon</v>
+        <v>Student 192</v>
       </c>
       <c r="C193" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>21CS193</v>
+        <v>22ECE018</v>
       </c>
       <c r="B194" t="str">
-        <v>Vihaan Bose</v>
+        <v>Student 193</v>
       </c>
       <c r="C194" t="str">
         <v>L</v>
@@ -2535,21 +2535,21 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>21CS194</v>
+        <v>22ECE019</v>
       </c>
       <c r="B195" t="str">
-        <v>Vihaan Kumar</v>
+        <v>Student 194</v>
       </c>
       <c r="C195" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>21CS195</v>
+        <v>22ECE020</v>
       </c>
       <c r="B196" t="str">
-        <v>Siddharth Dutta</v>
+        <v>Student 195</v>
       </c>
       <c r="C196" t="str">
         <v>L</v>
@@ -2557,21 +2557,21 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>21CS196</v>
+        <v>22ECE021</v>
       </c>
       <c r="B197" t="str">
-        <v>Arjun Pillai</v>
+        <v>Student 196</v>
       </c>
       <c r="C197" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>21CS197</v>
+        <v>22ECE022</v>
       </c>
       <c r="B198" t="str">
-        <v>Diya Verma</v>
+        <v>Student 197</v>
       </c>
       <c r="C198" t="str">
         <v>L</v>
@@ -2579,21 +2579,21 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>21CS198</v>
+        <v>22ECE023</v>
       </c>
       <c r="B199" t="str">
-        <v>Vihaan Pillai</v>
+        <v>Student 198</v>
       </c>
       <c r="C199" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>21CS199</v>
+        <v>22ECE024</v>
       </c>
       <c r="B200" t="str">
-        <v>Ishaan Kumar</v>
+        <v>Student 199</v>
       </c>
       <c r="C200" t="str">
         <v>L</v>
@@ -2601,21 +2601,21 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>21CS200</v>
+        <v>22ECE025</v>
       </c>
       <c r="B201" t="str">
-        <v>Anjali Sharma</v>
+        <v>Student 200</v>
       </c>
       <c r="C201" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>21CS201</v>
+        <v>22MECH001</v>
       </c>
       <c r="B202" t="str">
-        <v>Aditi Desai</v>
+        <v>Student 201</v>
       </c>
       <c r="C202" t="str">
         <v>L</v>
@@ -2623,21 +2623,21 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>21CS202</v>
+        <v>22MECH002</v>
       </c>
       <c r="B203" t="str">
-        <v>Siddharth Das</v>
+        <v>Student 202</v>
       </c>
       <c r="C203" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>21CS203</v>
+        <v>22MECH003</v>
       </c>
       <c r="B204" t="str">
-        <v>Vikram Rathore</v>
+        <v>Student 203</v>
       </c>
       <c r="C204" t="str">
         <v>L</v>
@@ -2645,21 +2645,21 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>21CS204</v>
+        <v>22MECH004</v>
       </c>
       <c r="B205" t="str">
-        <v>Krish Sharma</v>
+        <v>Student 204</v>
       </c>
       <c r="C205" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>21CS205</v>
+        <v>22MECH005</v>
       </c>
       <c r="B206" t="str">
-        <v>Zara Gupta</v>
+        <v>Student 205</v>
       </c>
       <c r="C206" t="str">
         <v>L</v>
@@ -2667,21 +2667,21 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>21CS206</v>
+        <v>22MECH006</v>
       </c>
       <c r="B207" t="str">
-        <v>Rahul Mishra</v>
+        <v>Student 206</v>
       </c>
       <c r="C207" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>21CS207</v>
+        <v>22MECH007</v>
       </c>
       <c r="B208" t="str">
-        <v>Amit Bose</v>
+        <v>Student 207</v>
       </c>
       <c r="C208" t="str">
         <v>L</v>
@@ -2689,21 +2689,21 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>21CS208</v>
+        <v>22MECH008</v>
       </c>
       <c r="B209" t="str">
-        <v>Aditi Desai</v>
+        <v>Student 208</v>
       </c>
       <c r="C209" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>21CS209</v>
+        <v>22MECH009</v>
       </c>
       <c r="B210" t="str">
-        <v>Sanya Ghosh</v>
+        <v>Student 209</v>
       </c>
       <c r="C210" t="str">
         <v>L</v>
@@ -2711,21 +2711,21 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>21CS210</v>
+        <v>22MECH010</v>
       </c>
       <c r="B211" t="str">
-        <v>Swati Yadav</v>
+        <v>Student 210</v>
       </c>
       <c r="C211" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>21CS211</v>
+        <v>22MECH011</v>
       </c>
       <c r="B212" t="str">
-        <v>Zara Patel</v>
+        <v>Student 211</v>
       </c>
       <c r="C212" t="str">
         <v>L</v>
@@ -2733,21 +2733,21 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>21CS212</v>
+        <v>22MECH012</v>
       </c>
       <c r="B213" t="str">
-        <v>Vikram Sharma</v>
+        <v>Student 212</v>
       </c>
       <c r="C213" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>21CS213</v>
+        <v>22MECH013</v>
       </c>
       <c r="B214" t="str">
-        <v>Riya Bose</v>
+        <v>Student 213</v>
       </c>
       <c r="C214" t="str">
         <v>L</v>
@@ -2755,21 +2755,21 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>21CS214</v>
+        <v>22MECH014</v>
       </c>
       <c r="B215" t="str">
-        <v>Aditi Das</v>
+        <v>Student 214</v>
       </c>
       <c r="C215" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>21CS215</v>
+        <v>22MECH015</v>
       </c>
       <c r="B216" t="str">
-        <v>Pooja Singh</v>
+        <v>Student 215</v>
       </c>
       <c r="C216" t="str">
         <v>L</v>
@@ -2777,21 +2777,21 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>21CS216</v>
+        <v>22MECH016</v>
       </c>
       <c r="B217" t="str">
-        <v>Aarav Nair</v>
+        <v>Student 216</v>
       </c>
       <c r="C217" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>21CS217</v>
+        <v>22MECH017</v>
       </c>
       <c r="B218" t="str">
-        <v>Krish Dutta</v>
+        <v>Student 217</v>
       </c>
       <c r="C218" t="str">
         <v>L</v>
@@ -2799,21 +2799,21 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>21CS218</v>
+        <v>22MECH018</v>
       </c>
       <c r="B219" t="str">
-        <v>Rohan Patel</v>
+        <v>Student 218</v>
       </c>
       <c r="C219" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>21CS219</v>
+        <v>22MECH019</v>
       </c>
       <c r="B220" t="str">
-        <v>Tarun Yadav</v>
+        <v>Student 219</v>
       </c>
       <c r="C220" t="str">
         <v>L</v>
@@ -2821,21 +2821,21 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>21CS220</v>
+        <v>22MECH020</v>
       </c>
       <c r="B221" t="str">
-        <v>Rohan Bose</v>
+        <v>Student 220</v>
       </c>
       <c r="C221" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>21CS221</v>
+        <v>22MECH021</v>
       </c>
       <c r="B222" t="str">
-        <v>Aditi Gupta</v>
+        <v>Student 221</v>
       </c>
       <c r="C222" t="str">
         <v>L</v>
@@ -2843,21 +2843,21 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>21CS222</v>
+        <v>22MECH022</v>
       </c>
       <c r="B223" t="str">
-        <v>Tarun Menon</v>
+        <v>Student 222</v>
       </c>
       <c r="C223" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>21CS223</v>
+        <v>22MECH023</v>
       </c>
       <c r="B224" t="str">
-        <v>Riya Rathore</v>
+        <v>Student 223</v>
       </c>
       <c r="C224" t="str">
         <v>L</v>
@@ -2865,21 +2865,21 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>21CS224</v>
+        <v>22MECH024</v>
       </c>
       <c r="B225" t="str">
-        <v>Priya Nair</v>
+        <v>Student 224</v>
       </c>
       <c r="C225" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>21CS225</v>
+        <v>22MECH025</v>
       </c>
       <c r="B226" t="str">
-        <v>Aditi Verma</v>
+        <v>Student 225</v>
       </c>
       <c r="C226" t="str">
         <v>L</v>
@@ -2887,21 +2887,21 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>21CS226</v>
+        <v>22CIVIL001</v>
       </c>
       <c r="B227" t="str">
-        <v>Aarav Gupta</v>
+        <v>Student 226</v>
       </c>
       <c r="C227" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>21CS227</v>
+        <v>22CIVIL002</v>
       </c>
       <c r="B228" t="str">
-        <v>Priya Desai</v>
+        <v>Student 227</v>
       </c>
       <c r="C228" t="str">
         <v>L</v>
@@ -2909,21 +2909,21 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>21CS228</v>
+        <v>22CIVIL003</v>
       </c>
       <c r="B229" t="str">
-        <v>Amit Dutta</v>
+        <v>Student 228</v>
       </c>
       <c r="C229" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>21CS229</v>
+        <v>22CIVIL004</v>
       </c>
       <c r="B230" t="str">
-        <v>Neha Singh</v>
+        <v>Student 229</v>
       </c>
       <c r="C230" t="str">
         <v>L</v>
@@ -2931,21 +2931,21 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>21CS230</v>
+        <v>22CIVIL005</v>
       </c>
       <c r="B231" t="str">
-        <v>Pranav Pillai</v>
+        <v>Student 230</v>
       </c>
       <c r="C231" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>21CS231</v>
+        <v>22CIVIL006</v>
       </c>
       <c r="B232" t="str">
-        <v>Karan Dutta</v>
+        <v>Student 231</v>
       </c>
       <c r="C232" t="str">
         <v>L</v>
@@ -2953,21 +2953,21 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>21CS232</v>
+        <v>22CIVIL007</v>
       </c>
       <c r="B233" t="str">
-        <v>Sanya Menon</v>
+        <v>Student 232</v>
       </c>
       <c r="C233" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>21CS233</v>
+        <v>22CIVIL008</v>
       </c>
       <c r="B234" t="str">
-        <v>Aditi Pillai</v>
+        <v>Student 233</v>
       </c>
       <c r="C234" t="str">
         <v>L</v>
@@ -2975,21 +2975,21 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>21CS234</v>
+        <v>22CIVIL009</v>
       </c>
       <c r="B235" t="str">
-        <v>Pooja Iyer</v>
+        <v>Student 234</v>
       </c>
       <c r="C235" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>21CS235</v>
+        <v>22CIVIL010</v>
       </c>
       <c r="B236" t="str">
-        <v>Vikram Dutta</v>
+        <v>Student 235</v>
       </c>
       <c r="C236" t="str">
         <v>L</v>
@@ -2997,21 +2997,21 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>21CS236</v>
+        <v>22CIVIL011</v>
       </c>
       <c r="B237" t="str">
-        <v>Amit Sharma</v>
+        <v>Student 236</v>
       </c>
       <c r="C237" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>21CS237</v>
+        <v>22CIVIL012</v>
       </c>
       <c r="B238" t="str">
-        <v>Tarun Nair</v>
+        <v>Student 237</v>
       </c>
       <c r="C238" t="str">
         <v>L</v>
@@ -3019,21 +3019,21 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>21CS238</v>
+        <v>22CIVIL013</v>
       </c>
       <c r="B239" t="str">
-        <v>Swati Ghosh</v>
+        <v>Student 238</v>
       </c>
       <c r="C239" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>21CS239</v>
+        <v>22CIVIL014</v>
       </c>
       <c r="B240" t="str">
-        <v>Krish Dutta</v>
+        <v>Student 239</v>
       </c>
       <c r="C240" t="str">
         <v>L</v>
@@ -3041,21 +3041,21 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>21CS240</v>
+        <v>22CIVIL015</v>
       </c>
       <c r="B241" t="str">
-        <v>Amit Rao</v>
+        <v>Student 240</v>
       </c>
       <c r="C241" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>21CS241</v>
+        <v>22CIVIL016</v>
       </c>
       <c r="B242" t="str">
-        <v>Pranav Rathore</v>
+        <v>Student 241</v>
       </c>
       <c r="C242" t="str">
         <v>L</v>
@@ -3063,21 +3063,21 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>21CS242</v>
+        <v>22CIVIL017</v>
       </c>
       <c r="B243" t="str">
-        <v>Vikram Das</v>
+        <v>Student 242</v>
       </c>
       <c r="C243" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>21CS243</v>
+        <v>22CIVIL018</v>
       </c>
       <c r="B244" t="str">
-        <v>Ishaan Verma</v>
+        <v>Student 243</v>
       </c>
       <c r="C244" t="str">
         <v>L</v>
@@ -3085,21 +3085,21 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>21CS244</v>
+        <v>22CIVIL019</v>
       </c>
       <c r="B245" t="str">
-        <v>Priya Verma</v>
+        <v>Student 244</v>
       </c>
       <c r="C245" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>21CS245</v>
+        <v>22CIVIL020</v>
       </c>
       <c r="B246" t="str">
-        <v>Arjun Sharma</v>
+        <v>Student 245</v>
       </c>
       <c r="C246" t="str">
         <v>L</v>
@@ -3107,21 +3107,21 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>21CS246</v>
+        <v>22CIVIL021</v>
       </c>
       <c r="B247" t="str">
-        <v>Arjun Rathore</v>
+        <v>Student 246</v>
       </c>
       <c r="C247" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>21CS247</v>
+        <v>22CIVIL022</v>
       </c>
       <c r="B248" t="str">
-        <v>Aditi Iyer</v>
+        <v>Student 247</v>
       </c>
       <c r="C248" t="str">
         <v>L</v>
@@ -3129,21 +3129,21 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>21CS248</v>
+        <v>22CIVIL023</v>
       </c>
       <c r="B249" t="str">
-        <v>Diya Chauhan</v>
+        <v>Student 248</v>
       </c>
       <c r="C249" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>21CS249</v>
+        <v>22CIVIL024</v>
       </c>
       <c r="B250" t="str">
-        <v>Aarav Kumar</v>
+        <v>Student 249</v>
       </c>
       <c r="C250" t="str">
         <v>L</v>
@@ -3151,32 +3151,32 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>21CS250</v>
+        <v>22CIVIL025</v>
       </c>
       <c r="B251" t="str">
-        <v>Pooja Dutta</v>
+        <v>Student 250</v>
       </c>
       <c r="C251" t="str">
-        <v>L</v>
+        <v>R</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>21EC001</v>
+        <v>23CS001</v>
       </c>
       <c r="B252" t="str">
-        <v>Aditi Bhatt</v>
+        <v>Student 251</v>
       </c>
       <c r="C252" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>21EC002</v>
+        <v>23CS002</v>
       </c>
       <c r="B253" t="str">
-        <v>Sneha Bhatt</v>
+        <v>Student 252</v>
       </c>
       <c r="C253" t="str">
         <v>R</v>
@@ -3184,21 +3184,21 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>21EC003</v>
+        <v>23CS003</v>
       </c>
       <c r="B254" t="str">
-        <v>Krish Joshi</v>
+        <v>Student 253</v>
       </c>
       <c r="C254" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>21EC004</v>
+        <v>23CS004</v>
       </c>
       <c r="B255" t="str">
-        <v>Vihaan Chauhan</v>
+        <v>Student 254</v>
       </c>
       <c r="C255" t="str">
         <v>R</v>
@@ -3206,21 +3206,21 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>21EC005</v>
+        <v>23CS005</v>
       </c>
       <c r="B256" t="str">
-        <v>Krish Gupta</v>
+        <v>Student 255</v>
       </c>
       <c r="C256" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>21EC006</v>
+        <v>23CS006</v>
       </c>
       <c r="B257" t="str">
-        <v>Rohan Das</v>
+        <v>Student 256</v>
       </c>
       <c r="C257" t="str">
         <v>R</v>
@@ -3228,21 +3228,21 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>21EC007</v>
+        <v>23CS007</v>
       </c>
       <c r="B258" t="str">
-        <v>Neha Singh</v>
+        <v>Student 257</v>
       </c>
       <c r="C258" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>21EC008</v>
+        <v>23CS008</v>
       </c>
       <c r="B259" t="str">
-        <v>Amit Sen</v>
+        <v>Student 258</v>
       </c>
       <c r="C259" t="str">
         <v>R</v>
@@ -3250,21 +3250,21 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>21EC009</v>
+        <v>23CS009</v>
       </c>
       <c r="B260" t="str">
-        <v>Sanya Joshi</v>
+        <v>Student 259</v>
       </c>
       <c r="C260" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>21EC010</v>
+        <v>23CS010</v>
       </c>
       <c r="B261" t="str">
-        <v>Vikram Patel</v>
+        <v>Student 260</v>
       </c>
       <c r="C261" t="str">
         <v>R</v>
@@ -3272,21 +3272,21 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>21EC011</v>
+        <v>23CS011</v>
       </c>
       <c r="B262" t="str">
-        <v>Siddharth Patel</v>
+        <v>Student 261</v>
       </c>
       <c r="C262" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>21EC012</v>
+        <v>23CS012</v>
       </c>
       <c r="B263" t="str">
-        <v>Rohan Yadav</v>
+        <v>Student 262</v>
       </c>
       <c r="C263" t="str">
         <v>R</v>
@@ -3294,21 +3294,21 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>21EC013</v>
+        <v>23CS013</v>
       </c>
       <c r="B264" t="str">
-        <v>Anjali Bhatt</v>
+        <v>Student 263</v>
       </c>
       <c r="C264" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>21EC014</v>
+        <v>23CS014</v>
       </c>
       <c r="B265" t="str">
-        <v>Aarav Singh</v>
+        <v>Student 264</v>
       </c>
       <c r="C265" t="str">
         <v>R</v>
@@ -3316,21 +3316,21 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>21EC015</v>
+        <v>23CS015</v>
       </c>
       <c r="B266" t="str">
-        <v>Pranav Yadav</v>
+        <v>Student 265</v>
       </c>
       <c r="C266" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>21EC016</v>
+        <v>23CS016</v>
       </c>
       <c r="B267" t="str">
-        <v>Sanya Reddy</v>
+        <v>Student 266</v>
       </c>
       <c r="C267" t="str">
         <v>R</v>
@@ -3338,21 +3338,21 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>21EC017</v>
+        <v>23CS017</v>
       </c>
       <c r="B268" t="str">
-        <v>Karan Sharma</v>
+        <v>Student 267</v>
       </c>
       <c r="C268" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>21EC018</v>
+        <v>23CS018</v>
       </c>
       <c r="B269" t="str">
-        <v>Rahul Das</v>
+        <v>Student 268</v>
       </c>
       <c r="C269" t="str">
         <v>R</v>
@@ -3360,21 +3360,21 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>21EC019</v>
+        <v>23CS019</v>
       </c>
       <c r="B270" t="str">
-        <v>Kavya Iyer</v>
+        <v>Student 269</v>
       </c>
       <c r="C270" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>21EC020</v>
+        <v>23CS020</v>
       </c>
       <c r="B271" t="str">
-        <v>Sneha Chauhan</v>
+        <v>Student 270</v>
       </c>
       <c r="C271" t="str">
         <v>R</v>
@@ -3382,21 +3382,21 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>21EC021</v>
+        <v>23CS021</v>
       </c>
       <c r="B272" t="str">
-        <v>Sneha Bhatt</v>
+        <v>Student 271</v>
       </c>
       <c r="C272" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>21EC022</v>
+        <v>23CS022</v>
       </c>
       <c r="B273" t="str">
-        <v>Amit Rao</v>
+        <v>Student 272</v>
       </c>
       <c r="C273" t="str">
         <v>R</v>
@@ -3404,21 +3404,21 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>21EC023</v>
+        <v>23CS023</v>
       </c>
       <c r="B274" t="str">
-        <v>Kavya Chauhan</v>
+        <v>Student 273</v>
       </c>
       <c r="C274" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>21EC024</v>
+        <v>23CS024</v>
       </c>
       <c r="B275" t="str">
-        <v>Riya Chauhan</v>
+        <v>Student 274</v>
       </c>
       <c r="C275" t="str">
         <v>R</v>
@@ -3426,21 +3426,21 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>21EC025</v>
+        <v>23CS025</v>
       </c>
       <c r="B276" t="str">
-        <v>Amit Singh</v>
+        <v>Student 275</v>
       </c>
       <c r="C276" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>21EC026</v>
+        <v>23IT001</v>
       </c>
       <c r="B277" t="str">
-        <v>Arjun Rao</v>
+        <v>Student 276</v>
       </c>
       <c r="C277" t="str">
         <v>R</v>
@@ -3448,21 +3448,21 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>21EC027</v>
+        <v>23IT002</v>
       </c>
       <c r="B278" t="str">
-        <v>Priya Rathore</v>
+        <v>Student 277</v>
       </c>
       <c r="C278" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>21EC028</v>
+        <v>23IT003</v>
       </c>
       <c r="B279" t="str">
-        <v>Swati Das</v>
+        <v>Student 278</v>
       </c>
       <c r="C279" t="str">
         <v>R</v>
@@ -3470,21 +3470,21 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>21EC029</v>
+        <v>23IT004</v>
       </c>
       <c r="B280" t="str">
-        <v>Zara Ghosh</v>
+        <v>Student 279</v>
       </c>
       <c r="C280" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>21EC030</v>
+        <v>23IT005</v>
       </c>
       <c r="B281" t="str">
-        <v>Ishaan Dutta</v>
+        <v>Student 280</v>
       </c>
       <c r="C281" t="str">
         <v>R</v>
@@ -3492,21 +3492,21 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>21EC031</v>
+        <v>23IT006</v>
       </c>
       <c r="B282" t="str">
-        <v>Kavya Ghosh</v>
+        <v>Student 281</v>
       </c>
       <c r="C282" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>21EC032</v>
+        <v>23IT007</v>
       </c>
       <c r="B283" t="str">
-        <v>Vihaan Joshi</v>
+        <v>Student 282</v>
       </c>
       <c r="C283" t="str">
         <v>R</v>
@@ -3514,21 +3514,21 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>21EC033</v>
+        <v>23IT008</v>
       </c>
       <c r="B284" t="str">
-        <v>Priya Ghosh</v>
+        <v>Student 283</v>
       </c>
       <c r="C284" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>21EC034</v>
+        <v>23IT009</v>
       </c>
       <c r="B285" t="str">
-        <v>Vihaan Pillai</v>
+        <v>Student 284</v>
       </c>
       <c r="C285" t="str">
         <v>R</v>
@@ -3536,21 +3536,21 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>21EC035</v>
+        <v>23IT010</v>
       </c>
       <c r="B286" t="str">
-        <v>Neha Rathore</v>
+        <v>Student 285</v>
       </c>
       <c r="C286" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>21EC036</v>
+        <v>23IT011</v>
       </c>
       <c r="B287" t="str">
-        <v>Neha Singh</v>
+        <v>Student 286</v>
       </c>
       <c r="C287" t="str">
         <v>R</v>
@@ -3558,21 +3558,21 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>21EC037</v>
+        <v>23IT012</v>
       </c>
       <c r="B288" t="str">
-        <v>Kavya Mishra</v>
+        <v>Student 287</v>
       </c>
       <c r="C288" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>21EC038</v>
+        <v>23IT013</v>
       </c>
       <c r="B289" t="str">
-        <v>Kavya Das</v>
+        <v>Student 288</v>
       </c>
       <c r="C289" t="str">
         <v>R</v>
@@ -3580,21 +3580,21 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>21EC039</v>
+        <v>23IT014</v>
       </c>
       <c r="B290" t="str">
-        <v>Swati Mishra</v>
+        <v>Student 289</v>
       </c>
       <c r="C290" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>21EC040</v>
+        <v>23IT015</v>
       </c>
       <c r="B291" t="str">
-        <v>Rahul Menon</v>
+        <v>Student 290</v>
       </c>
       <c r="C291" t="str">
         <v>R</v>
@@ -3602,21 +3602,21 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>21EC041</v>
+        <v>23IT016</v>
       </c>
       <c r="B292" t="str">
-        <v>Diya Nair</v>
+        <v>Student 291</v>
       </c>
       <c r="C292" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>21EC042</v>
+        <v>23IT017</v>
       </c>
       <c r="B293" t="str">
-        <v>Diya Bose</v>
+        <v>Student 292</v>
       </c>
       <c r="C293" t="str">
         <v>R</v>
@@ -3624,21 +3624,21 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>21EC043</v>
+        <v>23IT018</v>
       </c>
       <c r="B294" t="str">
-        <v>Pooja Verma</v>
+        <v>Student 293</v>
       </c>
       <c r="C294" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>21EC044</v>
+        <v>23IT019</v>
       </c>
       <c r="B295" t="str">
-        <v>Zara Singh</v>
+        <v>Student 294</v>
       </c>
       <c r="C295" t="str">
         <v>R</v>
@@ -3646,21 +3646,21 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>21EC045</v>
+        <v>23IT020</v>
       </c>
       <c r="B296" t="str">
-        <v>Sneha Pillai</v>
+        <v>Student 295</v>
       </c>
       <c r="C296" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>21EC046</v>
+        <v>23IT021</v>
       </c>
       <c r="B297" t="str">
-        <v>Pooja Desai</v>
+        <v>Student 296</v>
       </c>
       <c r="C297" t="str">
         <v>R</v>
@@ -3668,21 +3668,21 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>21EC047</v>
+        <v>23IT022</v>
       </c>
       <c r="B298" t="str">
-        <v>Neha Kumar</v>
+        <v>Student 297</v>
       </c>
       <c r="C298" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>21EC048</v>
+        <v>23IT023</v>
       </c>
       <c r="B299" t="str">
-        <v>Pranav Joshi</v>
+        <v>Student 298</v>
       </c>
       <c r="C299" t="str">
         <v>R</v>
@@ -3690,21 +3690,21 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>21EC049</v>
+        <v>23IT024</v>
       </c>
       <c r="B300" t="str">
-        <v>Riya Yadav</v>
+        <v>Student 299</v>
       </c>
       <c r="C300" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>21EC050</v>
+        <v>23IT025</v>
       </c>
       <c r="B301" t="str">
-        <v>Rahul Desai</v>
+        <v>Student 300</v>
       </c>
       <c r="C301" t="str">
         <v>R</v>
@@ -3712,21 +3712,21 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>21EC051</v>
+        <v>23ECE001</v>
       </c>
       <c r="B302" t="str">
-        <v>Karan Dutta</v>
+        <v>Student 301</v>
       </c>
       <c r="C302" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>21EC052</v>
+        <v>23ECE002</v>
       </c>
       <c r="B303" t="str">
-        <v>Sneha Kumar</v>
+        <v>Student 302</v>
       </c>
       <c r="C303" t="str">
         <v>R</v>
@@ -3734,21 +3734,21 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>21EC053</v>
+        <v>23ECE003</v>
       </c>
       <c r="B304" t="str">
-        <v>Kavya Chauhan</v>
+        <v>Student 303</v>
       </c>
       <c r="C304" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>21EC054</v>
+        <v>23ECE004</v>
       </c>
       <c r="B305" t="str">
-        <v>Amit Pillai</v>
+        <v>Student 304</v>
       </c>
       <c r="C305" t="str">
         <v>R</v>
@@ -3756,21 +3756,21 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>21EC055</v>
+        <v>23ECE005</v>
       </c>
       <c r="B306" t="str">
-        <v>Sneha Singh</v>
+        <v>Student 305</v>
       </c>
       <c r="C306" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>21EC056</v>
+        <v>23ECE006</v>
       </c>
       <c r="B307" t="str">
-        <v>Swati Bhatt</v>
+        <v>Student 306</v>
       </c>
       <c r="C307" t="str">
         <v>R</v>
@@ -3778,21 +3778,21 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>21EC057</v>
+        <v>23ECE007</v>
       </c>
       <c r="B308" t="str">
-        <v>Neha Kumar</v>
+        <v>Student 307</v>
       </c>
       <c r="C308" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>21EC058</v>
+        <v>23ECE008</v>
       </c>
       <c r="B309" t="str">
-        <v>Vihaan Ghosh</v>
+        <v>Student 308</v>
       </c>
       <c r="C309" t="str">
         <v>R</v>
@@ -3800,21 +3800,21 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>21EC059</v>
+        <v>23ECE009</v>
       </c>
       <c r="B310" t="str">
-        <v>Amit Reddy</v>
+        <v>Student 309</v>
       </c>
       <c r="C310" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>21EC060</v>
+        <v>23ECE010</v>
       </c>
       <c r="B311" t="str">
-        <v>Arjun Rao</v>
+        <v>Student 310</v>
       </c>
       <c r="C311" t="str">
         <v>R</v>
@@ -3822,21 +3822,21 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>21EC061</v>
+        <v>23ECE011</v>
       </c>
       <c r="B312" t="str">
-        <v>Anjali Yadav</v>
+        <v>Student 311</v>
       </c>
       <c r="C312" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>21EC062</v>
+        <v>23ECE012</v>
       </c>
       <c r="B313" t="str">
-        <v>Kavya Patel</v>
+        <v>Student 312</v>
       </c>
       <c r="C313" t="str">
         <v>R</v>
@@ -3844,21 +3844,21 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>21EC063</v>
+        <v>23ECE013</v>
       </c>
       <c r="B314" t="str">
-        <v>Diya Mishra</v>
+        <v>Student 313</v>
       </c>
       <c r="C314" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>21EC064</v>
+        <v>23ECE014</v>
       </c>
       <c r="B315" t="str">
-        <v>Ishaan Iyer</v>
+        <v>Student 314</v>
       </c>
       <c r="C315" t="str">
         <v>R</v>
@@ -3866,21 +3866,21 @@
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>21EC065</v>
+        <v>23ECE015</v>
       </c>
       <c r="B316" t="str">
-        <v>Ishaan Rao</v>
+        <v>Student 315</v>
       </c>
       <c r="C316" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>21EC066</v>
+        <v>23ECE016</v>
       </c>
       <c r="B317" t="str">
-        <v>Vikram Mishra</v>
+        <v>Student 316</v>
       </c>
       <c r="C317" t="str">
         <v>R</v>
@@ -3888,21 +3888,21 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>21EC067</v>
+        <v>23ECE017</v>
       </c>
       <c r="B318" t="str">
-        <v>Swati Rathore</v>
+        <v>Student 317</v>
       </c>
       <c r="C318" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>21EC068</v>
+        <v>23ECE018</v>
       </c>
       <c r="B319" t="str">
-        <v>Swati Gupta</v>
+        <v>Student 318</v>
       </c>
       <c r="C319" t="str">
         <v>R</v>
@@ -3910,21 +3910,21 @@
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>21EC069</v>
+        <v>23ECE019</v>
       </c>
       <c r="B320" t="str">
-        <v>Aarav Verma</v>
+        <v>Student 319</v>
       </c>
       <c r="C320" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>21EC070</v>
+        <v>23ECE020</v>
       </c>
       <c r="B321" t="str">
-        <v>Amit Mishra</v>
+        <v>Student 320</v>
       </c>
       <c r="C321" t="str">
         <v>R</v>
@@ -3932,21 +3932,21 @@
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>21EC071</v>
+        <v>23ECE021</v>
       </c>
       <c r="B322" t="str">
-        <v>Anjali Rao</v>
+        <v>Student 321</v>
       </c>
       <c r="C322" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>21EC072</v>
+        <v>23ECE022</v>
       </c>
       <c r="B323" t="str">
-        <v>Tarun Menon</v>
+        <v>Student 322</v>
       </c>
       <c r="C323" t="str">
         <v>R</v>
@@ -3954,21 +3954,21 @@
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>21EC073</v>
+        <v>23ECE023</v>
       </c>
       <c r="B324" t="str">
-        <v>Vikram Reddy</v>
+        <v>Student 323</v>
       </c>
       <c r="C324" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>21EC074</v>
+        <v>23ECE024</v>
       </c>
       <c r="B325" t="str">
-        <v>Aarav Joshi</v>
+        <v>Student 324</v>
       </c>
       <c r="C325" t="str">
         <v>R</v>
@@ -3976,21 +3976,21 @@
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>21EC075</v>
+        <v>23ECE025</v>
       </c>
       <c r="B326" t="str">
-        <v>Zara Pillai</v>
+        <v>Student 325</v>
       </c>
       <c r="C326" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>21EC076</v>
+        <v>23MECH001</v>
       </c>
       <c r="B327" t="str">
-        <v>Swati Patel</v>
+        <v>Student 326</v>
       </c>
       <c r="C327" t="str">
         <v>R</v>
@@ -3998,21 +3998,21 @@
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>21EC077</v>
+        <v>23MECH002</v>
       </c>
       <c r="B328" t="str">
-        <v>Tarun Das</v>
+        <v>Student 327</v>
       </c>
       <c r="C328" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>21EC078</v>
+        <v>23MECH003</v>
       </c>
       <c r="B329" t="str">
-        <v>Aditi Singh</v>
+        <v>Student 328</v>
       </c>
       <c r="C329" t="str">
         <v>R</v>
@@ -4020,21 +4020,21 @@
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>21EC079</v>
+        <v>23MECH004</v>
       </c>
       <c r="B330" t="str">
-        <v>Neha Mishra</v>
+        <v>Student 329</v>
       </c>
       <c r="C330" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>21EC080</v>
+        <v>23MECH005</v>
       </c>
       <c r="B331" t="str">
-        <v>Tarun Gupta</v>
+        <v>Student 330</v>
       </c>
       <c r="C331" t="str">
         <v>R</v>
@@ -4042,21 +4042,21 @@
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>21EC081</v>
+        <v>23MECH006</v>
       </c>
       <c r="B332" t="str">
-        <v>Anjali Mishra</v>
+        <v>Student 331</v>
       </c>
       <c r="C332" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>21EC082</v>
+        <v>23MECH007</v>
       </c>
       <c r="B333" t="str">
-        <v>Karan Verma</v>
+        <v>Student 332</v>
       </c>
       <c r="C333" t="str">
         <v>R</v>
@@ -4064,21 +4064,21 @@
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>21EC083</v>
+        <v>23MECH008</v>
       </c>
       <c r="B334" t="str">
-        <v>Arjun Gupta</v>
+        <v>Student 333</v>
       </c>
       <c r="C334" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>21EC084</v>
+        <v>23MECH009</v>
       </c>
       <c r="B335" t="str">
-        <v>Zara Pillai</v>
+        <v>Student 334</v>
       </c>
       <c r="C335" t="str">
         <v>R</v>
@@ -4086,21 +4086,21 @@
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>21EC085</v>
+        <v>23MECH010</v>
       </c>
       <c r="B336" t="str">
-        <v>Aarav Menon</v>
+        <v>Student 335</v>
       </c>
       <c r="C336" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>21EC086</v>
+        <v>23MECH011</v>
       </c>
       <c r="B337" t="str">
-        <v>Amit Reddy</v>
+        <v>Student 336</v>
       </c>
       <c r="C337" t="str">
         <v>R</v>
@@ -4108,21 +4108,21 @@
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>21EC087</v>
+        <v>23MECH012</v>
       </c>
       <c r="B338" t="str">
-        <v>Tarun Nair</v>
+        <v>Student 337</v>
       </c>
       <c r="C338" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>21EC088</v>
+        <v>23MECH013</v>
       </c>
       <c r="B339" t="str">
-        <v>Rohan Kumar</v>
+        <v>Student 338</v>
       </c>
       <c r="C339" t="str">
         <v>R</v>
@@ -4130,21 +4130,21 @@
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>21EC089</v>
+        <v>23MECH014</v>
       </c>
       <c r="B340" t="str">
-        <v>Amit Kumar</v>
+        <v>Student 339</v>
       </c>
       <c r="C340" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>21EC090</v>
+        <v>23MECH015</v>
       </c>
       <c r="B341" t="str">
-        <v>Riya Sharma</v>
+        <v>Student 340</v>
       </c>
       <c r="C341" t="str">
         <v>R</v>
@@ -4152,21 +4152,21 @@
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>21EC091</v>
+        <v>23MECH016</v>
       </c>
       <c r="B342" t="str">
-        <v>Rahul Das</v>
+        <v>Student 341</v>
       </c>
       <c r="C342" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>21EC092</v>
+        <v>23MECH017</v>
       </c>
       <c r="B343" t="str">
-        <v>Vihaan Singh</v>
+        <v>Student 342</v>
       </c>
       <c r="C343" t="str">
         <v>R</v>
@@ -4174,21 +4174,21 @@
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>21EC093</v>
+        <v>23MECH018</v>
       </c>
       <c r="B344" t="str">
-        <v>Tarun Gupta</v>
+        <v>Student 343</v>
       </c>
       <c r="C344" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>21EC094</v>
+        <v>23MECH019</v>
       </c>
       <c r="B345" t="str">
-        <v>Amit Kumar</v>
+        <v>Student 344</v>
       </c>
       <c r="C345" t="str">
         <v>R</v>
@@ -4196,21 +4196,21 @@
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>21EC095</v>
+        <v>23MECH020</v>
       </c>
       <c r="B346" t="str">
-        <v>Swati Mishra</v>
+        <v>Student 345</v>
       </c>
       <c r="C346" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>21EC096</v>
+        <v>23MECH021</v>
       </c>
       <c r="B347" t="str">
-        <v>Rohan Gupta</v>
+        <v>Student 346</v>
       </c>
       <c r="C347" t="str">
         <v>R</v>
@@ -4218,21 +4218,21 @@
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>21EC097</v>
+        <v>23MECH022</v>
       </c>
       <c r="B348" t="str">
-        <v>Arjun Nair</v>
+        <v>Student 347</v>
       </c>
       <c r="C348" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>21EC098</v>
+        <v>23MECH023</v>
       </c>
       <c r="B349" t="str">
-        <v>Zara Das</v>
+        <v>Student 348</v>
       </c>
       <c r="C349" t="str">
         <v>R</v>
@@ -4240,21 +4240,21 @@
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>21EC099</v>
+        <v>23MECH024</v>
       </c>
       <c r="B350" t="str">
-        <v>Vihaan Desai</v>
+        <v>Student 349</v>
       </c>
       <c r="C350" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>21EC100</v>
+        <v>23MECH025</v>
       </c>
       <c r="B351" t="str">
-        <v>Amit Kumar</v>
+        <v>Student 350</v>
       </c>
       <c r="C351" t="str">
         <v>R</v>
@@ -4262,21 +4262,21 @@
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>21EC101</v>
+        <v>23CIVIL001</v>
       </c>
       <c r="B352" t="str">
-        <v>Tarun Singh</v>
+        <v>Student 351</v>
       </c>
       <c r="C352" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>21EC102</v>
+        <v>23CIVIL002</v>
       </c>
       <c r="B353" t="str">
-        <v>Amit Verma</v>
+        <v>Student 352</v>
       </c>
       <c r="C353" t="str">
         <v>R</v>
@@ -4284,21 +4284,21 @@
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>21EC103</v>
+        <v>23CIVIL003</v>
       </c>
       <c r="B354" t="str">
-        <v>Riya Yadav</v>
+        <v>Student 353</v>
       </c>
       <c r="C354" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>21EC104</v>
+        <v>23CIVIL004</v>
       </c>
       <c r="B355" t="str">
-        <v>Vikram Das</v>
+        <v>Student 354</v>
       </c>
       <c r="C355" t="str">
         <v>R</v>
@@ -4306,21 +4306,21 @@
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>21EC105</v>
+        <v>23CIVIL005</v>
       </c>
       <c r="B356" t="str">
-        <v>Amit Sharma</v>
+        <v>Student 355</v>
       </c>
       <c r="C356" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>21EC106</v>
+        <v>23CIVIL006</v>
       </c>
       <c r="B357" t="str">
-        <v>Diya Mishra</v>
+        <v>Student 356</v>
       </c>
       <c r="C357" t="str">
         <v>R</v>
@@ -4328,21 +4328,21 @@
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>21EC107</v>
+        <v>23CIVIL007</v>
       </c>
       <c r="B358" t="str">
-        <v>Ishaan Rathore</v>
+        <v>Student 357</v>
       </c>
       <c r="C358" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>21EC108</v>
+        <v>23CIVIL008</v>
       </c>
       <c r="B359" t="str">
-        <v>Sneha Iyer</v>
+        <v>Student 358</v>
       </c>
       <c r="C359" t="str">
         <v>R</v>
@@ -4350,21 +4350,21 @@
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>21EC109</v>
+        <v>23CIVIL009</v>
       </c>
       <c r="B360" t="str">
-        <v>Rohan Kumar</v>
+        <v>Student 359</v>
       </c>
       <c r="C360" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>21EC110</v>
+        <v>23CIVIL010</v>
       </c>
       <c r="B361" t="str">
-        <v>Siddharth Kumar</v>
+        <v>Student 360</v>
       </c>
       <c r="C361" t="str">
         <v>R</v>
@@ -4372,21 +4372,21 @@
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>21EC111</v>
+        <v>23CIVIL011</v>
       </c>
       <c r="B362" t="str">
-        <v>Sneha Mishra</v>
+        <v>Student 361</v>
       </c>
       <c r="C362" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>21EC112</v>
+        <v>23CIVIL012</v>
       </c>
       <c r="B363" t="str">
-        <v>Karan Gupta</v>
+        <v>Student 362</v>
       </c>
       <c r="C363" t="str">
         <v>R</v>
@@ -4394,21 +4394,21 @@
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>21EC113</v>
+        <v>23CIVIL013</v>
       </c>
       <c r="B364" t="str">
-        <v>Aditi Gupta</v>
+        <v>Student 363</v>
       </c>
       <c r="C364" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>21EC114</v>
+        <v>23CIVIL014</v>
       </c>
       <c r="B365" t="str">
-        <v>Priya Rathore</v>
+        <v>Student 364</v>
       </c>
       <c r="C365" t="str">
         <v>R</v>
@@ -4416,21 +4416,21 @@
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>21EC115</v>
+        <v>23CIVIL015</v>
       </c>
       <c r="B366" t="str">
-        <v>Arjun Rao</v>
+        <v>Student 365</v>
       </c>
       <c r="C366" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>21EC116</v>
+        <v>23CIVIL016</v>
       </c>
       <c r="B367" t="str">
-        <v>Krish Mishra</v>
+        <v>Student 366</v>
       </c>
       <c r="C367" t="str">
         <v>R</v>
@@ -4438,21 +4438,21 @@
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>21EC117</v>
+        <v>23CIVIL017</v>
       </c>
       <c r="B368" t="str">
-        <v>Vikram Mishra</v>
+        <v>Student 367</v>
       </c>
       <c r="C368" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>21EC118</v>
+        <v>23CIVIL018</v>
       </c>
       <c r="B369" t="str">
-        <v>Priya Sen</v>
+        <v>Student 368</v>
       </c>
       <c r="C369" t="str">
         <v>R</v>
@@ -4460,21 +4460,21 @@
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>21EC119</v>
+        <v>23CIVIL019</v>
       </c>
       <c r="B370" t="str">
-        <v>Aarav Yadav</v>
+        <v>Student 369</v>
       </c>
       <c r="C370" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>21EC120</v>
+        <v>23CIVIL020</v>
       </c>
       <c r="B371" t="str">
-        <v>Rohan Dutta</v>
+        <v>Student 370</v>
       </c>
       <c r="C371" t="str">
         <v>R</v>
@@ -4482,21 +4482,21 @@
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>21EC121</v>
+        <v>23CIVIL021</v>
       </c>
       <c r="B372" t="str">
-        <v>Vikram Desai</v>
+        <v>Student 371</v>
       </c>
       <c r="C372" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>21EC122</v>
+        <v>23CIVIL022</v>
       </c>
       <c r="B373" t="str">
-        <v>Priya Singh</v>
+        <v>Student 372</v>
       </c>
       <c r="C373" t="str">
         <v>R</v>
@@ -4504,21 +4504,21 @@
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>21EC123</v>
+        <v>23CIVIL023</v>
       </c>
       <c r="B374" t="str">
-        <v>Diya Verma</v>
+        <v>Student 373</v>
       </c>
       <c r="C374" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>21EC124</v>
+        <v>23CIVIL024</v>
       </c>
       <c r="B375" t="str">
-        <v>Tarun Yadav</v>
+        <v>Student 374</v>
       </c>
       <c r="C375" t="str">
         <v>R</v>
@@ -4526,21 +4526,21 @@
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>21EC125</v>
+        <v>23CIVIL025</v>
       </c>
       <c r="B376" t="str">
-        <v>Sanya Sharma</v>
+        <v>Student 375</v>
       </c>
       <c r="C376" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>21EC126</v>
+        <v>24CS001</v>
       </c>
       <c r="B377" t="str">
-        <v>Vikram Sen</v>
+        <v>Student 376</v>
       </c>
       <c r="C377" t="str">
         <v>R</v>
@@ -4548,21 +4548,21 @@
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>21EC127</v>
+        <v>24CS002</v>
       </c>
       <c r="B378" t="str">
-        <v>Arjun Singh</v>
+        <v>Student 377</v>
       </c>
       <c r="C378" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>21EC128</v>
+        <v>24CS003</v>
       </c>
       <c r="B379" t="str">
-        <v>Siddharth Pillai</v>
+        <v>Student 378</v>
       </c>
       <c r="C379" t="str">
         <v>R</v>
@@ -4570,21 +4570,21 @@
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>21EC129</v>
+        <v>24CS004</v>
       </c>
       <c r="B380" t="str">
-        <v>Ishaan Mishra</v>
+        <v>Student 379</v>
       </c>
       <c r="C380" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>21EC130</v>
+        <v>24CS005</v>
       </c>
       <c r="B381" t="str">
-        <v>Aditi Sharma</v>
+        <v>Student 380</v>
       </c>
       <c r="C381" t="str">
         <v>R</v>
@@ -4592,21 +4592,21 @@
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>21EC131</v>
+        <v>24CS006</v>
       </c>
       <c r="B382" t="str">
-        <v>Ishaan Das</v>
+        <v>Student 381</v>
       </c>
       <c r="C382" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>21EC132</v>
+        <v>24CS007</v>
       </c>
       <c r="B383" t="str">
-        <v>Rahul Das</v>
+        <v>Student 382</v>
       </c>
       <c r="C383" t="str">
         <v>R</v>
@@ -4614,21 +4614,21 @@
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>21EC133</v>
+        <v>24CS008</v>
       </c>
       <c r="B384" t="str">
-        <v>Siddharth Pillai</v>
+        <v>Student 383</v>
       </c>
       <c r="C384" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>21EC134</v>
+        <v>24CS009</v>
       </c>
       <c r="B385" t="str">
-        <v>Zara Das</v>
+        <v>Student 384</v>
       </c>
       <c r="C385" t="str">
         <v>R</v>
@@ -4636,21 +4636,21 @@
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>21EC135</v>
+        <v>24CS010</v>
       </c>
       <c r="B386" t="str">
-        <v>Riya Dutta</v>
+        <v>Student 385</v>
       </c>
       <c r="C386" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>21EC136</v>
+        <v>24CS011</v>
       </c>
       <c r="B387" t="str">
-        <v>Priya Pillai</v>
+        <v>Student 386</v>
       </c>
       <c r="C387" t="str">
         <v>R</v>
@@ -4658,21 +4658,21 @@
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>21EC137</v>
+        <v>24CS012</v>
       </c>
       <c r="B388" t="str">
-        <v>Krish Chauhan</v>
+        <v>Student 387</v>
       </c>
       <c r="C388" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>21EC138</v>
+        <v>24CS013</v>
       </c>
       <c r="B389" t="str">
-        <v>Vikram Rao</v>
+        <v>Student 388</v>
       </c>
       <c r="C389" t="str">
         <v>R</v>
@@ -4680,21 +4680,21 @@
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>21EC139</v>
+        <v>24CS014</v>
       </c>
       <c r="B390" t="str">
-        <v>Arjun Singh</v>
+        <v>Student 389</v>
       </c>
       <c r="C390" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>21EC140</v>
+        <v>24CS015</v>
       </c>
       <c r="B391" t="str">
-        <v>Ishaan Sharma</v>
+        <v>Student 390</v>
       </c>
       <c r="C391" t="str">
         <v>R</v>
@@ -4702,21 +4702,21 @@
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>21EC141</v>
+        <v>24CS016</v>
       </c>
       <c r="B392" t="str">
-        <v>Neha Menon</v>
+        <v>Student 391</v>
       </c>
       <c r="C392" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>21EC142</v>
+        <v>24CS017</v>
       </c>
       <c r="B393" t="str">
-        <v>Vikram Das</v>
+        <v>Student 392</v>
       </c>
       <c r="C393" t="str">
         <v>R</v>
@@ -4724,21 +4724,21 @@
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>21EC143</v>
+        <v>24CS018</v>
       </c>
       <c r="B394" t="str">
-        <v>Karan Kumar</v>
+        <v>Student 393</v>
       </c>
       <c r="C394" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>21EC144</v>
+        <v>24CS019</v>
       </c>
       <c r="B395" t="str">
-        <v>Aditi Verma</v>
+        <v>Student 394</v>
       </c>
       <c r="C395" t="str">
         <v>R</v>
@@ -4746,21 +4746,21 @@
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>21EC145</v>
+        <v>24CS020</v>
       </c>
       <c r="B396" t="str">
-        <v>Tarun Ghosh</v>
+        <v>Student 395</v>
       </c>
       <c r="C396" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>21EC146</v>
+        <v>24CS021</v>
       </c>
       <c r="B397" t="str">
-        <v>Vihaan Bhatt</v>
+        <v>Student 396</v>
       </c>
       <c r="C397" t="str">
         <v>R</v>
@@ -4768,21 +4768,21 @@
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>21EC147</v>
+        <v>24CS022</v>
       </c>
       <c r="B398" t="str">
-        <v>Neha Chauhan</v>
+        <v>Student 397</v>
       </c>
       <c r="C398" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>21EC148</v>
+        <v>24CS023</v>
       </c>
       <c r="B399" t="str">
-        <v>Pooja Sen</v>
+        <v>Student 398</v>
       </c>
       <c r="C399" t="str">
         <v>R</v>
@@ -4790,21 +4790,21 @@
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>21EC149</v>
+        <v>24CS024</v>
       </c>
       <c r="B400" t="str">
-        <v>Swati Sen</v>
+        <v>Student 399</v>
       </c>
       <c r="C400" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>21EC150</v>
+        <v>24CS025</v>
       </c>
       <c r="B401" t="str">
-        <v>Aarav Sen</v>
+        <v>Student 400</v>
       </c>
       <c r="C401" t="str">
         <v>R</v>
@@ -4812,21 +4812,21 @@
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>21EC151</v>
+        <v>24IT001</v>
       </c>
       <c r="B402" t="str">
-        <v>Ishaan Gupta</v>
+        <v>Student 401</v>
       </c>
       <c r="C402" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>21EC152</v>
+        <v>24IT002</v>
       </c>
       <c r="B403" t="str">
-        <v>Siddharth Reddy</v>
+        <v>Student 402</v>
       </c>
       <c r="C403" t="str">
         <v>R</v>
@@ -4834,21 +4834,21 @@
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>21EC153</v>
+        <v>24IT003</v>
       </c>
       <c r="B404" t="str">
-        <v>Amit Singh</v>
+        <v>Student 403</v>
       </c>
       <c r="C404" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>21EC154</v>
+        <v>24IT004</v>
       </c>
       <c r="B405" t="str">
-        <v>Vikram Desai</v>
+        <v>Student 404</v>
       </c>
       <c r="C405" t="str">
         <v>R</v>
@@ -4856,21 +4856,21 @@
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>21EC155</v>
+        <v>24IT005</v>
       </c>
       <c r="B406" t="str">
-        <v>Diya Menon</v>
+        <v>Student 405</v>
       </c>
       <c r="C406" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>21EC156</v>
+        <v>24IT006</v>
       </c>
       <c r="B407" t="str">
-        <v>Aarav Desai</v>
+        <v>Student 406</v>
       </c>
       <c r="C407" t="str">
         <v>R</v>
@@ -4878,21 +4878,21 @@
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>21EC157</v>
+        <v>24IT007</v>
       </c>
       <c r="B408" t="str">
-        <v>Rohan Yadav</v>
+        <v>Student 407</v>
       </c>
       <c r="C408" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>21EC158</v>
+        <v>24IT008</v>
       </c>
       <c r="B409" t="str">
-        <v>Rohan Sen</v>
+        <v>Student 408</v>
       </c>
       <c r="C409" t="str">
         <v>R</v>
@@ -4900,21 +4900,21 @@
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>21EC159</v>
+        <v>24IT009</v>
       </c>
       <c r="B410" t="str">
-        <v>Zara Reddy</v>
+        <v>Student 409</v>
       </c>
       <c r="C410" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>21EC160</v>
+        <v>24IT010</v>
       </c>
       <c r="B411" t="str">
-        <v>Swati Patel</v>
+        <v>Student 410</v>
       </c>
       <c r="C411" t="str">
         <v>R</v>
@@ -4922,21 +4922,21 @@
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>21EC161</v>
+        <v>24IT011</v>
       </c>
       <c r="B412" t="str">
-        <v>Pranav Rathore</v>
+        <v>Student 411</v>
       </c>
       <c r="C412" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>21EC162</v>
+        <v>24IT012</v>
       </c>
       <c r="B413" t="str">
-        <v>Tarun Kumar</v>
+        <v>Student 412</v>
       </c>
       <c r="C413" t="str">
         <v>R</v>
@@ -4944,21 +4944,21 @@
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>21EC163</v>
+        <v>24IT013</v>
       </c>
       <c r="B414" t="str">
-        <v>Kavya Yadav</v>
+        <v>Student 413</v>
       </c>
       <c r="C414" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>21EC164</v>
+        <v>24IT014</v>
       </c>
       <c r="B415" t="str">
-        <v>Arjun Nair</v>
+        <v>Student 414</v>
       </c>
       <c r="C415" t="str">
         <v>R</v>
@@ -4966,21 +4966,21 @@
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>21EC165</v>
+        <v>24IT015</v>
       </c>
       <c r="B416" t="str">
-        <v>Arjun Singh</v>
+        <v>Student 415</v>
       </c>
       <c r="C416" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>21EC166</v>
+        <v>24IT016</v>
       </c>
       <c r="B417" t="str">
-        <v>Amit Dutta</v>
+        <v>Student 416</v>
       </c>
       <c r="C417" t="str">
         <v>R</v>
@@ -4988,21 +4988,21 @@
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>21EC167</v>
+        <v>24IT017</v>
       </c>
       <c r="B418" t="str">
-        <v>Amit Desai</v>
+        <v>Student 417</v>
       </c>
       <c r="C418" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>21EC168</v>
+        <v>24IT018</v>
       </c>
       <c r="B419" t="str">
-        <v>Sneha Sharma</v>
+        <v>Student 418</v>
       </c>
       <c r="C419" t="str">
         <v>R</v>
@@ -5010,21 +5010,21 @@
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>21EC169</v>
+        <v>24IT019</v>
       </c>
       <c r="B420" t="str">
-        <v>Anjali Yadav</v>
+        <v>Student 419</v>
       </c>
       <c r="C420" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>21EC170</v>
+        <v>24IT020</v>
       </c>
       <c r="B421" t="str">
-        <v>Diya Chauhan</v>
+        <v>Student 420</v>
       </c>
       <c r="C421" t="str">
         <v>R</v>
@@ -5032,21 +5032,21 @@
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>21EC171</v>
+        <v>24IT021</v>
       </c>
       <c r="B422" t="str">
-        <v>Kavya Nair</v>
+        <v>Student 421</v>
       </c>
       <c r="C422" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>21EC172</v>
+        <v>24IT022</v>
       </c>
       <c r="B423" t="str">
-        <v>Karan Rao</v>
+        <v>Student 422</v>
       </c>
       <c r="C423" t="str">
         <v>R</v>
@@ -5054,21 +5054,21 @@
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>21EC173</v>
+        <v>24IT023</v>
       </c>
       <c r="B424" t="str">
-        <v>Amit Reddy</v>
+        <v>Student 423</v>
       </c>
       <c r="C424" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>21EC174</v>
+        <v>24IT024</v>
       </c>
       <c r="B425" t="str">
-        <v>Vikram Rathore</v>
+        <v>Student 424</v>
       </c>
       <c r="C425" t="str">
         <v>R</v>
@@ -5076,21 +5076,21 @@
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>21EC175</v>
+        <v>24IT025</v>
       </c>
       <c r="B426" t="str">
-        <v>Krish Rao</v>
+        <v>Student 425</v>
       </c>
       <c r="C426" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>21EC176</v>
+        <v>24ECE001</v>
       </c>
       <c r="B427" t="str">
-        <v>Riya Gupta</v>
+        <v>Student 426</v>
       </c>
       <c r="C427" t="str">
         <v>R</v>
@@ -5098,21 +5098,21 @@
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>21EC177</v>
+        <v>24ECE002</v>
       </c>
       <c r="B428" t="str">
-        <v>Amit Das</v>
+        <v>Student 427</v>
       </c>
       <c r="C428" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>21EC178</v>
+        <v>24ECE003</v>
       </c>
       <c r="B429" t="str">
-        <v>Rohan Nair</v>
+        <v>Student 428</v>
       </c>
       <c r="C429" t="str">
         <v>R</v>
@@ -5120,21 +5120,21 @@
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>21EC179</v>
+        <v>24ECE004</v>
       </c>
       <c r="B430" t="str">
-        <v>Amit Mishra</v>
+        <v>Student 429</v>
       </c>
       <c r="C430" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>21EC180</v>
+        <v>24ECE005</v>
       </c>
       <c r="B431" t="str">
-        <v>Aditi Das</v>
+        <v>Student 430</v>
       </c>
       <c r="C431" t="str">
         <v>R</v>
@@ -5142,21 +5142,21 @@
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>21EC181</v>
+        <v>24ECE006</v>
       </c>
       <c r="B432" t="str">
-        <v>Anjali Mishra</v>
+        <v>Student 431</v>
       </c>
       <c r="C432" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>21EC182</v>
+        <v>24ECE007</v>
       </c>
       <c r="B433" t="str">
-        <v>Kavya Bose</v>
+        <v>Student 432</v>
       </c>
       <c r="C433" t="str">
         <v>R</v>
@@ -5164,21 +5164,21 @@
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>21EC183</v>
+        <v>24ECE008</v>
       </c>
       <c r="B434" t="str">
-        <v>Anjali Chauhan</v>
+        <v>Student 433</v>
       </c>
       <c r="C434" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>21EC184</v>
+        <v>24ECE009</v>
       </c>
       <c r="B435" t="str">
-        <v>Pranav Rathore</v>
+        <v>Student 434</v>
       </c>
       <c r="C435" t="str">
         <v>R</v>
@@ -5186,21 +5186,21 @@
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>21EC185</v>
+        <v>24ECE010</v>
       </c>
       <c r="B436" t="str">
-        <v>Neha Mishra</v>
+        <v>Student 435</v>
       </c>
       <c r="C436" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>21EC186</v>
+        <v>24ECE011</v>
       </c>
       <c r="B437" t="str">
-        <v>Sneha Joshi</v>
+        <v>Student 436</v>
       </c>
       <c r="C437" t="str">
         <v>R</v>
@@ -5208,21 +5208,21 @@
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>21EC187</v>
+        <v>24ECE012</v>
       </c>
       <c r="B438" t="str">
-        <v>Zara Singh</v>
+        <v>Student 437</v>
       </c>
       <c r="C438" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>21EC188</v>
+        <v>24ECE013</v>
       </c>
       <c r="B439" t="str">
-        <v>Anjali Chauhan</v>
+        <v>Student 438</v>
       </c>
       <c r="C439" t="str">
         <v>R</v>
@@ -5230,21 +5230,21 @@
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>21EC189</v>
+        <v>24ECE014</v>
       </c>
       <c r="B440" t="str">
-        <v>Arjun Nair</v>
+        <v>Student 439</v>
       </c>
       <c r="C440" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>21EC190</v>
+        <v>24ECE015</v>
       </c>
       <c r="B441" t="str">
-        <v>Arjun Reddy</v>
+        <v>Student 440</v>
       </c>
       <c r="C441" t="str">
         <v>R</v>
@@ -5252,21 +5252,21 @@
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>21EC191</v>
+        <v>24ECE016</v>
       </c>
       <c r="B442" t="str">
-        <v>Vihaan Das</v>
+        <v>Student 441</v>
       </c>
       <c r="C442" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>21EC192</v>
+        <v>24ECE017</v>
       </c>
       <c r="B443" t="str">
-        <v>Siddharth Menon</v>
+        <v>Student 442</v>
       </c>
       <c r="C443" t="str">
         <v>R</v>
@@ -5274,21 +5274,21 @@
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>21EC193</v>
+        <v>24ECE018</v>
       </c>
       <c r="B444" t="str">
-        <v>Zara Yadav</v>
+        <v>Student 443</v>
       </c>
       <c r="C444" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>21EC194</v>
+        <v>24ECE019</v>
       </c>
       <c r="B445" t="str">
-        <v>Arjun Rao</v>
+        <v>Student 444</v>
       </c>
       <c r="C445" t="str">
         <v>R</v>
@@ -5296,21 +5296,21 @@
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>21EC195</v>
+        <v>24ECE020</v>
       </c>
       <c r="B446" t="str">
-        <v>Aarav Rao</v>
+        <v>Student 445</v>
       </c>
       <c r="C446" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>21EC196</v>
+        <v>24ECE021</v>
       </c>
       <c r="B447" t="str">
-        <v>Neha Rao</v>
+        <v>Student 446</v>
       </c>
       <c r="C447" t="str">
         <v>R</v>
@@ -5318,21 +5318,21 @@
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>21EC197</v>
+        <v>24ECE022</v>
       </c>
       <c r="B448" t="str">
-        <v>Sneha Verma</v>
+        <v>Student 447</v>
       </c>
       <c r="C448" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>21EC198</v>
+        <v>24ECE023</v>
       </c>
       <c r="B449" t="str">
-        <v>Ishaan Rathore</v>
+        <v>Student 448</v>
       </c>
       <c r="C449" t="str">
         <v>R</v>
@@ -5340,21 +5340,21 @@
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>21EC199</v>
+        <v>24ECE024</v>
       </c>
       <c r="B450" t="str">
-        <v>Rahul Singh</v>
+        <v>Student 449</v>
       </c>
       <c r="C450" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>21EC200</v>
+        <v>24ECE025</v>
       </c>
       <c r="B451" t="str">
-        <v>Neha Pillai</v>
+        <v>Student 450</v>
       </c>
       <c r="C451" t="str">
         <v>R</v>
@@ -5362,21 +5362,21 @@
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>21EC201</v>
+        <v>24MECH001</v>
       </c>
       <c r="B452" t="str">
-        <v>Krish Patel</v>
+        <v>Student 451</v>
       </c>
       <c r="C452" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>21EC202</v>
+        <v>24MECH002</v>
       </c>
       <c r="B453" t="str">
-        <v>Rahul Ghosh</v>
+        <v>Student 452</v>
       </c>
       <c r="C453" t="str">
         <v>R</v>
@@ -5384,21 +5384,21 @@
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>21EC203</v>
+        <v>24MECH003</v>
       </c>
       <c r="B454" t="str">
-        <v>Vihaan Kumar</v>
+        <v>Student 453</v>
       </c>
       <c r="C454" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>21EC204</v>
+        <v>24MECH004</v>
       </c>
       <c r="B455" t="str">
-        <v>Neha Sharma</v>
+        <v>Student 454</v>
       </c>
       <c r="C455" t="str">
         <v>R</v>
@@ -5406,21 +5406,21 @@
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>21EC205</v>
+        <v>24MECH005</v>
       </c>
       <c r="B456" t="str">
-        <v>Riya Rao</v>
+        <v>Student 455</v>
       </c>
       <c r="C456" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>21EC206</v>
+        <v>24MECH006</v>
       </c>
       <c r="B457" t="str">
-        <v>Priya Gupta</v>
+        <v>Student 456</v>
       </c>
       <c r="C457" t="str">
         <v>R</v>
@@ -5428,21 +5428,21 @@
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>21EC207</v>
+        <v>24MECH007</v>
       </c>
       <c r="B458" t="str">
-        <v>Vihaan Nair</v>
+        <v>Student 457</v>
       </c>
       <c r="C458" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>21EC208</v>
+        <v>24MECH008</v>
       </c>
       <c r="B459" t="str">
-        <v>Arjun Kumar</v>
+        <v>Student 458</v>
       </c>
       <c r="C459" t="str">
         <v>R</v>
@@ -5450,21 +5450,21 @@
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>21EC209</v>
+        <v>24MECH009</v>
       </c>
       <c r="B460" t="str">
-        <v>Rohan Bhatt</v>
+        <v>Student 459</v>
       </c>
       <c r="C460" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>21EC210</v>
+        <v>24MECH010</v>
       </c>
       <c r="B461" t="str">
-        <v>Rohan Rao</v>
+        <v>Student 460</v>
       </c>
       <c r="C461" t="str">
         <v>R</v>
@@ -5472,21 +5472,21 @@
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>21EC211</v>
+        <v>24MECH011</v>
       </c>
       <c r="B462" t="str">
-        <v>Swati Sen</v>
+        <v>Student 461</v>
       </c>
       <c r="C462" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>21EC212</v>
+        <v>24MECH012</v>
       </c>
       <c r="B463" t="str">
-        <v>Vihaan Desai</v>
+        <v>Student 462</v>
       </c>
       <c r="C463" t="str">
         <v>R</v>
@@ -5494,21 +5494,21 @@
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>21EC213</v>
+        <v>24MECH013</v>
       </c>
       <c r="B464" t="str">
-        <v>Karan Pillai</v>
+        <v>Student 463</v>
       </c>
       <c r="C464" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>21EC214</v>
+        <v>24MECH014</v>
       </c>
       <c r="B465" t="str">
-        <v>Vikram Desai</v>
+        <v>Student 464</v>
       </c>
       <c r="C465" t="str">
         <v>R</v>
@@ -5516,21 +5516,21 @@
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>21EC215</v>
+        <v>24MECH015</v>
       </c>
       <c r="B466" t="str">
-        <v>Amit Chauhan</v>
+        <v>Student 465</v>
       </c>
       <c r="C466" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>21EC216</v>
+        <v>24MECH016</v>
       </c>
       <c r="B467" t="str">
-        <v>Diya Chauhan</v>
+        <v>Student 466</v>
       </c>
       <c r="C467" t="str">
         <v>R</v>
@@ -5538,21 +5538,21 @@
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>21EC217</v>
+        <v>24MECH017</v>
       </c>
       <c r="B468" t="str">
-        <v>Rohan Dutta</v>
+        <v>Student 467</v>
       </c>
       <c r="C468" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>21EC218</v>
+        <v>24MECH018</v>
       </c>
       <c r="B469" t="str">
-        <v>Tarun Sharma</v>
+        <v>Student 468</v>
       </c>
       <c r="C469" t="str">
         <v>R</v>
@@ -5560,21 +5560,21 @@
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>21EC219</v>
+        <v>24MECH019</v>
       </c>
       <c r="B470" t="str">
-        <v>Aditi Patel</v>
+        <v>Student 469</v>
       </c>
       <c r="C470" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>21EC220</v>
+        <v>24MECH020</v>
       </c>
       <c r="B471" t="str">
-        <v>Anjali Singh</v>
+        <v>Student 470</v>
       </c>
       <c r="C471" t="str">
         <v>R</v>
@@ -5582,21 +5582,21 @@
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>21EC221</v>
+        <v>24MECH021</v>
       </c>
       <c r="B472" t="str">
-        <v>Arjun Chauhan</v>
+        <v>Student 471</v>
       </c>
       <c r="C472" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>21EC222</v>
+        <v>24MECH022</v>
       </c>
       <c r="B473" t="str">
-        <v>Karan Rao</v>
+        <v>Student 472</v>
       </c>
       <c r="C473" t="str">
         <v>R</v>
@@ -5604,21 +5604,21 @@
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>21EC223</v>
+        <v>24MECH023</v>
       </c>
       <c r="B474" t="str">
-        <v>Sneha Bhatt</v>
+        <v>Student 473</v>
       </c>
       <c r="C474" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>21EC224</v>
+        <v>24MECH024</v>
       </c>
       <c r="B475" t="str">
-        <v>Sanya Das</v>
+        <v>Student 474</v>
       </c>
       <c r="C475" t="str">
         <v>R</v>
@@ -5626,21 +5626,21 @@
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>21EC225</v>
+        <v>24MECH025</v>
       </c>
       <c r="B476" t="str">
-        <v>Zara Mishra</v>
+        <v>Student 475</v>
       </c>
       <c r="C476" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>21EC226</v>
+        <v>24CIVIL001</v>
       </c>
       <c r="B477" t="str">
-        <v>Vikram Desai</v>
+        <v>Student 476</v>
       </c>
       <c r="C477" t="str">
         <v>R</v>
@@ -5648,21 +5648,21 @@
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>21EC227</v>
+        <v>24CIVIL002</v>
       </c>
       <c r="B478" t="str">
-        <v>Riya Dutta</v>
+        <v>Student 477</v>
       </c>
       <c r="C478" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>21EC228</v>
+        <v>24CIVIL003</v>
       </c>
       <c r="B479" t="str">
-        <v>Karan Rathore</v>
+        <v>Student 478</v>
       </c>
       <c r="C479" t="str">
         <v>R</v>
@@ -5670,21 +5670,21 @@
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>21EC229</v>
+        <v>24CIVIL004</v>
       </c>
       <c r="B480" t="str">
-        <v>Siddharth Singh</v>
+        <v>Student 479</v>
       </c>
       <c r="C480" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>21EC230</v>
+        <v>24CIVIL005</v>
       </c>
       <c r="B481" t="str">
-        <v>Karan Rao</v>
+        <v>Student 480</v>
       </c>
       <c r="C481" t="str">
         <v>R</v>
@@ -5692,21 +5692,21 @@
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>21EC231</v>
+        <v>24CIVIL006</v>
       </c>
       <c r="B482" t="str">
-        <v>Zara Pillai</v>
+        <v>Student 481</v>
       </c>
       <c r="C482" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>21EC232</v>
+        <v>24CIVIL007</v>
       </c>
       <c r="B483" t="str">
-        <v>Pooja Chauhan</v>
+        <v>Student 482</v>
       </c>
       <c r="C483" t="str">
         <v>R</v>
@@ -5714,21 +5714,21 @@
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>21EC233</v>
+        <v>24CIVIL008</v>
       </c>
       <c r="B484" t="str">
-        <v>Sneha Iyer</v>
+        <v>Student 483</v>
       </c>
       <c r="C484" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>21EC234</v>
+        <v>24CIVIL009</v>
       </c>
       <c r="B485" t="str">
-        <v>Sanya Nair</v>
+        <v>Student 484</v>
       </c>
       <c r="C485" t="str">
         <v>R</v>
@@ -5736,21 +5736,21 @@
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>21EC235</v>
+        <v>24CIVIL010</v>
       </c>
       <c r="B486" t="str">
-        <v>Neha Verma</v>
+        <v>Student 485</v>
       </c>
       <c r="C486" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>21EC236</v>
+        <v>24CIVIL011</v>
       </c>
       <c r="B487" t="str">
-        <v>Sneha Reddy</v>
+        <v>Student 486</v>
       </c>
       <c r="C487" t="str">
         <v>R</v>
@@ -5758,21 +5758,21 @@
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>21EC237</v>
+        <v>24CIVIL012</v>
       </c>
       <c r="B488" t="str">
-        <v>Aditi Sharma</v>
+        <v>Student 487</v>
       </c>
       <c r="C488" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>21EC238</v>
+        <v>24CIVIL013</v>
       </c>
       <c r="B489" t="str">
-        <v>Pranav Sharma</v>
+        <v>Student 488</v>
       </c>
       <c r="C489" t="str">
         <v>R</v>
@@ -5780,21 +5780,21 @@
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>21EC239</v>
+        <v>24CIVIL014</v>
       </c>
       <c r="B490" t="str">
-        <v>Amit Verma</v>
+        <v>Student 489</v>
       </c>
       <c r="C490" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>21EC240</v>
+        <v>24CIVIL015</v>
       </c>
       <c r="B491" t="str">
-        <v>Rohan Yadav</v>
+        <v>Student 490</v>
       </c>
       <c r="C491" t="str">
         <v>R</v>
@@ -5802,21 +5802,21 @@
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>21EC241</v>
+        <v>24CIVIL016</v>
       </c>
       <c r="B492" t="str">
-        <v>Sanya Gupta</v>
+        <v>Student 491</v>
       </c>
       <c r="C492" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>21EC242</v>
+        <v>24CIVIL017</v>
       </c>
       <c r="B493" t="str">
-        <v>Ishaan Mishra</v>
+        <v>Student 492</v>
       </c>
       <c r="C493" t="str">
         <v>R</v>
@@ -5824,21 +5824,21 @@
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>21EC243</v>
+        <v>24CIVIL018</v>
       </c>
       <c r="B494" t="str">
-        <v>Ishaan Menon</v>
+        <v>Student 493</v>
       </c>
       <c r="C494" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>21EC244</v>
+        <v>24CIVIL019</v>
       </c>
       <c r="B495" t="str">
-        <v>Vihaan Reddy</v>
+        <v>Student 494</v>
       </c>
       <c r="C495" t="str">
         <v>R</v>
@@ -5846,21 +5846,21 @@
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>21EC245</v>
+        <v>24CIVIL020</v>
       </c>
       <c r="B496" t="str">
-        <v>Aditi Yadav</v>
+        <v>Student 495</v>
       </c>
       <c r="C496" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>21EC246</v>
+        <v>24CIVIL021</v>
       </c>
       <c r="B497" t="str">
-        <v>Zara Gupta</v>
+        <v>Student 496</v>
       </c>
       <c r="C497" t="str">
         <v>R</v>
@@ -5868,21 +5868,21 @@
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>21EC247</v>
+        <v>24CIVIL022</v>
       </c>
       <c r="B498" t="str">
-        <v>Aarav Gupta</v>
+        <v>Student 497</v>
       </c>
       <c r="C498" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>21EC248</v>
+        <v>24CIVIL023</v>
       </c>
       <c r="B499" t="str">
-        <v>Riya Dutta</v>
+        <v>Student 498</v>
       </c>
       <c r="C499" t="str">
         <v>R</v>
@@ -5890,21 +5890,21 @@
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>21EC249</v>
+        <v>24CIVIL024</v>
       </c>
       <c r="B500" t="str">
-        <v>Pooja Das</v>
+        <v>Student 499</v>
       </c>
       <c r="C500" t="str">
-        <v>R</v>
+        <v>L</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>21EC250</v>
+        <v>24CIVIL025</v>
       </c>
       <c r="B501" t="str">
-        <v>Rahul Joshi</v>
+        <v>Student 500</v>
       </c>
       <c r="C501" t="str">
         <v>R</v>
